--- a/excel_reports/backtest_compare/s2/compare_s2_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s2/compare_s2_M15_20260528_0800_20260608_1000.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:42:23</t>
+          <t>2026-06-18 16:58:13</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         <v>46170.75</v>
       </c>
       <c r="AF31" s="10" t="n">
-        <v>4386.49</v>
+        <v>4386.47</v>
       </c>
       <c r="AG31" s="10" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>4386.33</v>
       </c>
       <c r="AI31" s="10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="AJ31" s="10" t="inlineStr"/>
       <c r="AK31" s="10" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
         <v>46170.75</v>
       </c>
       <c r="AF2" s="10" t="n">
-        <v>4386.49</v>
+        <v>4386.47</v>
       </c>
       <c r="AG2" s="10" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>4386.33</v>
       </c>
       <c r="AI2" s="10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="AJ2" s="10" t="inlineStr"/>
       <c r="AK2" s="10" t="inlineStr"/>
@@ -11501,7 +11501,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="F20" s="13" t="n">
         <v>46170.60416666666</v>
@@ -11812,7 +11812,7 @@
         <v>5</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>35.68</v>
+        <v>35.66</v>
       </c>
       <c r="F31" s="13" t="n">
         <v>46170.60416666666</v>
@@ -12450,7 +12450,7 @@
         <v>3</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>42.42</v>
+        <v>42.4</v>
       </c>
       <c r="F53" s="13" t="n">
         <v>46170.60416666666</v>

--- a/excel_reports/backtest_compare/s2/compare_s2_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s2/compare_s2_M15_20260528_0800_20260608_1000.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Gap Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mismatches'!$A$1:$BK$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mismatches'!$A$1:$BK$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 16:58:13</t>
+          <t>2026-06-19 17:35:49</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.09</v>
+        <v>6.050000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-27.92</v>
+        <v>-27.76</v>
       </c>
     </row>
     <row r="20">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>43.01000000000001</v>
+        <v>33.81</v>
       </c>
     </row>
     <row r="22">
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK35"/>
+  <dimension ref="A1:BK37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -792,7 +792,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
@@ -1169,54 +1169,54 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>LOOSE_MATCH_SL_GUARD</t>
+          <t>PNL_DIFF_SAME_BUCKET</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>534643103</t>
+          <t>533469126</t>
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>46171.82914351852</v>
+        <v>46170.58363425926</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>46171.83998842593</v>
+        <v>46170.58751157407</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>4530.5775</v>
+        <v>4385.14</v>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H2" s="8" t="n">
-        <v>4534.57</v>
+        <v>4387.4</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>15.97</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>2.38</v>
+        <v>-2.26</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>3.62</v>
+        <v>-2.26</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>6.05</v>
+        <v>-2.26</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>3.92</v>
+        <v>-2.26</v>
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>[sl 4530.65]</t>
+          <t>[sl 4385.14]</t>
         </is>
       </c>
       <c r="O2" s="8" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="P2" s="8" t="inlineStr"/>
@@ -1234,24 +1234,24 @@
       <c r="AB2" s="8" t="inlineStr"/>
       <c r="AC2" s="8" t="inlineStr"/>
       <c r="AD2" s="9" t="n">
-        <v>46171.79166666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="AE2" s="9" t="n">
-        <v>46171.89583333334</v>
+        <v>46170.75</v>
       </c>
       <c r="AF2" s="8" t="n">
-        <v>4564.21</v>
+        <v>4386.49</v>
       </c>
       <c r="AG2" s="8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH2" s="8" t="n">
-        <v>4534.52</v>
+        <v>4386.33</v>
       </c>
       <c r="AI2" s="8" t="n">
-        <v>-29.69</v>
+        <v>0.16</v>
       </c>
       <c r="AJ2" s="8" t="inlineStr"/>
       <c r="AK2" s="8" t="inlineStr"/>
@@ -1259,28 +1259,28 @@
       <c r="AM2" s="8" t="inlineStr"/>
       <c r="AN2" s="8" t="inlineStr">
         <is>
-          <t>SL_GUARD_CLOSE</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO2" s="8" t="inlineStr">
         <is>
-          <t>LOOSE</t>
+          <t>NEAR</t>
         </is>
       </c>
       <c r="AP2" s="8" t="n">
-        <v>539.72</v>
+        <v>296.74</v>
       </c>
       <c r="AQ2" s="8" t="n">
-        <v>53.97</v>
+        <v>29.57</v>
       </c>
       <c r="AR2" s="8" t="n">
-        <v>0.05</v>
+        <v>1.07</v>
       </c>
       <c r="AS2" s="8" t="n">
-        <v>-33.63</v>
+        <v>-1.35</v>
       </c>
       <c r="AT2" s="8" t="n">
-        <v>45.66</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AU2" s="8" t="inlineStr"/>
       <c r="AV2" s="8" t="inlineStr"/>
@@ -1308,22 +1308,22 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>CLOSE_LIFECYCLE_PD</t>
+          <t>LOOSE_MATCH_SL_GUARD</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>533702297</t>
+          <t>534643103</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>46170.79517361111</v>
+        <v>46171.82914351852</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>46170.79518518518</v>
+        <v>46171.83998842593</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>4389.42</v>
+        <v>4530.5775</v>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
@@ -1331,31 +1331,31 @@
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>4389.2</v>
+        <v>4534.57</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>-0.88</v>
+        <v>15.97</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>-0.22</v>
+        <v>2.38</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>-0.22</v>
+        <v>3.62</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>-0.22</v>
+        <v>6.05</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>-0.22</v>
+        <v>3.92</v>
       </c>
       <c r="N3" s="8" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>[sl 4530.65]</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="P3" s="8" t="inlineStr"/>
@@ -1373,13 +1373,13 @@
       <c r="AB3" s="8" t="inlineStr"/>
       <c r="AC3" s="8" t="inlineStr"/>
       <c r="AD3" s="9" t="n">
-        <v>46170.75</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="AE3" s="9" t="n">
-        <v>46170.8125</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="AF3" s="8" t="n">
-        <v>4387.36</v>
+        <v>4564.21</v>
       </c>
       <c r="AG3" s="8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="AH3" s="8" t="n">
-        <v>4389.13</v>
+        <v>4534.52</v>
       </c>
       <c r="AI3" s="8" t="n">
-        <v>1.77</v>
+        <v>-29.69</v>
       </c>
       <c r="AJ3" s="8" t="inlineStr"/>
       <c r="AK3" s="8" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
       <c r="AM3" s="8" t="inlineStr"/>
       <c r="AN3" s="8" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="AO3" s="8" t="inlineStr">
@@ -1407,37 +1407,25 @@
         </is>
       </c>
       <c r="AP3" s="8" t="n">
-        <v>650.5700000000001</v>
+        <v>539.72</v>
       </c>
       <c r="AQ3" s="8" t="n">
-        <v>65.05</v>
+        <v>53.97</v>
       </c>
       <c r="AR3" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AS3" s="8" t="n">
-        <v>2.06</v>
+        <v>-33.63</v>
       </c>
       <c r="AT3" s="8" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="AU3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" s="8" t="n"/>
-      <c r="AW3" s="8" t="n">
-        <v>4387.36</v>
-      </c>
-      <c r="AX3" s="8" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="AY3" s="8" t="inlineStr">
-        <is>
-          <t>M5 4387.36</t>
-        </is>
-      </c>
+        <v>45.66</v>
+      </c>
+      <c r="AU3" s="8" t="inlineStr"/>
+      <c r="AV3" s="8" t="inlineStr"/>
+      <c r="AW3" s="8" t="inlineStr"/>
+      <c r="AX3" s="8" t="inlineStr"/>
+      <c r="AY3" s="8" t="inlineStr"/>
       <c r="AZ3" s="8" t="inlineStr"/>
       <c r="BA3" s="8" t="inlineStr"/>
       <c r="BB3" s="8" t="inlineStr"/>
@@ -1452,123 +1440,155 @@
       <c r="BK3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>LIVE_ONLY</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>533514424</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>46170.8722337963</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>46170.91012731481</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>4425.155</v>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>CLOSE_LIFECYCLE_PD</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>533702297</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>46170.79517361111</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>46170.79518518518</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>4389.42</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n">
-        <v>4426.98</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>7.300000000000002</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="M4" s="10" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4431.78]</t>
-        </is>
-      </c>
-      <c r="O4" s="10" t="inlineStr">
-        <is>
-          <t>[M30_H1_H4]_S2</t>
-        </is>
-      </c>
-      <c r="P4" s="10" t="inlineStr"/>
-      <c r="Q4" s="10" t="inlineStr"/>
-      <c r="R4" s="10" t="inlineStr"/>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="10" t="inlineStr"/>
-      <c r="U4" s="10" t="inlineStr"/>
-      <c r="V4" s="10" t="inlineStr"/>
-      <c r="W4" s="10" t="inlineStr"/>
-      <c r="X4" s="10" t="inlineStr"/>
-      <c r="Y4" s="10" t="inlineStr"/>
-      <c r="Z4" s="10" t="inlineStr"/>
-      <c r="AA4" s="10" t="inlineStr"/>
-      <c r="AB4" s="10" t="inlineStr"/>
-      <c r="AC4" s="10" t="inlineStr"/>
-      <c r="AD4" s="10" t="inlineStr"/>
-      <c r="AE4" s="10" t="inlineStr"/>
-      <c r="AF4" s="10" t="inlineStr"/>
-      <c r="AG4" s="10" t="inlineStr"/>
-      <c r="AH4" s="10" t="inlineStr"/>
-      <c r="AI4" s="10" t="inlineStr"/>
-      <c r="AJ4" s="10" t="inlineStr"/>
-      <c r="AK4" s="10" t="inlineStr"/>
-      <c r="AL4" s="10" t="inlineStr"/>
-      <c r="AM4" s="10" t="inlineStr"/>
-      <c r="AN4" s="10" t="inlineStr"/>
-      <c r="AO4" s="10" t="inlineStr"/>
-      <c r="AP4" s="10" t="inlineStr"/>
-      <c r="AQ4" s="10" t="inlineStr"/>
-      <c r="AR4" s="10" t="inlineStr"/>
-      <c r="AS4" s="10" t="inlineStr"/>
-      <c r="AT4" s="10" t="inlineStr"/>
-      <c r="AU4" s="10" t="inlineStr"/>
-      <c r="AV4" s="10" t="inlineStr"/>
-      <c r="AW4" s="10" t="inlineStr"/>
-      <c r="AX4" s="10" t="inlineStr"/>
-      <c r="AY4" s="10" t="inlineStr"/>
-      <c r="AZ4" s="10" t="inlineStr"/>
-      <c r="BA4" s="10" t="inlineStr"/>
-      <c r="BB4" s="11" t="n">
+      <c r="H4" s="8" t="n">
+        <v>4389.2</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>PD Zone fill che</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>[M5_M15]_S2</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="8" t="inlineStr"/>
+      <c r="V4" s="8" t="inlineStr"/>
+      <c r="W4" s="8" t="inlineStr"/>
+      <c r="X4" s="8" t="inlineStr"/>
+      <c r="Y4" s="8" t="inlineStr"/>
+      <c r="Z4" s="8" t="inlineStr"/>
+      <c r="AA4" s="8" t="inlineStr"/>
+      <c r="AB4" s="8" t="inlineStr"/>
+      <c r="AC4" s="8" t="inlineStr"/>
+      <c r="AD4" s="9" t="n">
         <v>46170.75</v>
       </c>
-      <c r="BC4" s="10" t="n">
+      <c r="AE4" s="9" t="n">
+        <v>46170.8125</v>
+      </c>
+      <c r="AF4" s="8" t="n">
+        <v>4387.36</v>
+      </c>
+      <c r="AG4" s="8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="AH4" s="8" t="n">
         <v>4389.13</v>
       </c>
-      <c r="BD4" s="10" t="inlineStr">
+      <c r="AI4" s="8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ4" s="8" t="inlineStr"/>
+      <c r="AK4" s="8" t="inlineStr"/>
+      <c r="AL4" s="8" t="inlineStr"/>
+      <c r="AM4" s="8" t="inlineStr"/>
+      <c r="AN4" s="8" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="BE4" s="10" t="n">
-        <v>176.02</v>
-      </c>
-      <c r="BF4" s="10" t="n">
-        <v>37.85</v>
-      </c>
-      <c r="BG4" s="10" t="inlineStr"/>
-      <c r="BH4" s="10" t="inlineStr"/>
-      <c r="BI4" s="10" t="inlineStr"/>
-      <c r="BJ4" s="10" t="inlineStr"/>
-      <c r="BK4" s="10" t="inlineStr"/>
+      <c r="AO4" s="8" t="inlineStr">
+        <is>
+          <t>LOOSE</t>
+        </is>
+      </c>
+      <c r="AP4" s="8" t="n">
+        <v>650.5700000000001</v>
+      </c>
+      <c r="AQ4" s="8" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="AR4" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AS4" s="8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT4" s="8" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="AU4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="8" t="n"/>
+      <c r="AW4" s="8" t="n">
+        <v>4387.36</v>
+      </c>
+      <c r="AX4" s="8" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="AY4" s="8" t="inlineStr">
+        <is>
+          <t>M5 4387.36</t>
+        </is>
+      </c>
+      <c r="AZ4" s="8" t="inlineStr"/>
+      <c r="BA4" s="8" t="inlineStr"/>
+      <c r="BB4" s="8" t="inlineStr"/>
+      <c r="BC4" s="8" t="inlineStr"/>
+      <c r="BD4" s="8" t="inlineStr"/>
+      <c r="BE4" s="8" t="inlineStr"/>
+      <c r="BF4" s="8" t="inlineStr"/>
+      <c r="BG4" s="8" t="inlineStr"/>
+      <c r="BH4" s="8" t="inlineStr"/>
+      <c r="BI4" s="8" t="inlineStr"/>
+      <c r="BJ4" s="8" t="inlineStr"/>
+      <c r="BK4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -1578,54 +1598,54 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>533235372</t>
+          <t>532987481</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46170.92326388889</v>
+        <v>46170.39285879629</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>46170.94454861111</v>
+        <v>46170.40341435185</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>4441.902499999999</v>
+        <v>4420.57</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>4440.51</v>
+        <v>4426.11</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>-5.57</v>
+        <v>-22.16</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>1.94</v>
+        <v>-5.54</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>3.42</v>
+        <v>-5.54</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>7.27</v>
+        <v>-5.54</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>-18.2</v>
+        <v>-5.54</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill rou</t>
+          <t>[sl 4420.57]</t>
         </is>
       </c>
       <c r="O5" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>[M15_H1]_S2</t>
         </is>
       </c>
       <c r="P5" s="10" t="inlineStr"/>
@@ -1667,10 +1687,10 @@
       <c r="AZ5" s="10" t="inlineStr"/>
       <c r="BA5" s="10" t="inlineStr"/>
       <c r="BB5" s="11" t="n">
-        <v>46170.75</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="BC5" s="10" t="n">
-        <v>4389.13</v>
+        <v>4386.33</v>
       </c>
       <c r="BD5" s="10" t="inlineStr">
         <is>
@@ -1678,10 +1698,10 @@
         </is>
       </c>
       <c r="BE5" s="10" t="n">
-        <v>249.5</v>
+        <v>304.28</v>
       </c>
       <c r="BF5" s="10" t="n">
-        <v>51.38</v>
+        <v>39.78</v>
       </c>
       <c r="BG5" s="10" t="inlineStr"/>
       <c r="BH5" s="10" t="inlineStr"/>
@@ -1697,22 +1717,22 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>533239894</t>
+          <t>533235372</t>
         </is>
       </c>
       <c r="D6" s="11" t="n">
         <v>46170.92326388889</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>46170.9480787037</v>
+        <v>46170.94454861111</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>4445.785</v>
+        <v>4441.902499999999</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -1720,31 +1740,31 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>4440.63</v>
+        <v>4440.51</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>-20.62</v>
+        <v>-5.57</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>3.69</v>
+        <v>3.42</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>7.38</v>
+        <v>7.27</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>-33.76</v>
+        <v>-18.2</v>
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>[sl 4474.39]</t>
+          <t>PD Zone fill rou</t>
         </is>
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr"/>
@@ -1800,7 +1820,7 @@
         <v>249.5</v>
       </c>
       <c r="BF6" s="10" t="n">
-        <v>51.5</v>
+        <v>51.38</v>
       </c>
       <c r="BG6" s="10" t="inlineStr"/>
       <c r="BH6" s="10" t="inlineStr"/>
@@ -1821,17 +1841,17 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>532607893</t>
+          <t>533239894</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>46170.94866898148</v>
+        <v>46170.92326388889</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>46170.95097222222</v>
+        <v>46170.9480787037</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>4466.74</v>
+        <v>4445.785</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
@@ -1839,31 +1859,31 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>4477.57</v>
+        <v>4440.63</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>43.32</v>
+        <v>-20.62</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>10.83</v>
+        <v>2.07</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>10.83</v>
+        <v>3.69</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>10.83</v>
+        <v>7.38</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>10.83</v>
+        <v>-33.76</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>[tp 4466.74]</t>
+          <t>[sl 4474.39]</t>
         </is>
       </c>
       <c r="O7" s="10" t="inlineStr">
         <is>
-          <t>[M1_M5_M15]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="P7" s="10" t="inlineStr"/>
@@ -1916,10 +1936,10 @@
         </is>
       </c>
       <c r="BE7" s="10" t="n">
-        <v>286.08</v>
+        <v>249.5</v>
       </c>
       <c r="BF7" s="10" t="n">
-        <v>88.44</v>
+        <v>51.5</v>
       </c>
       <c r="BG7" s="10" t="inlineStr"/>
       <c r="BH7" s="10" t="inlineStr"/>
@@ -1940,17 +1960,17 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>534211757</t>
+          <t>532607893</t>
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>46171.12677083333</v>
+        <v>46170.94866898148</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>46171.13321759259</v>
+        <v>46170.95097222222</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>4501.1125</v>
+        <v>4466.74</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -1958,31 +1978,31 @@
         </is>
       </c>
       <c r="H8" s="10" t="n">
-        <v>4503.68</v>
+        <v>4477.57</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>10.27</v>
+        <v>43.32</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>2.26</v>
+        <v>10.83</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>3.09</v>
+        <v>10.83</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>2.46</v>
+        <v>10.83</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>2.46</v>
+        <v>10.83</v>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>[sl 4501.22]</t>
+          <t>[tp 4466.74]</t>
         </is>
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>[M1_M5_M15]_S2</t>
         </is>
       </c>
       <c r="P8" s="10" t="inlineStr"/>
@@ -2035,10 +2055,10 @@
         </is>
       </c>
       <c r="BE8" s="10" t="n">
-        <v>542.55</v>
+        <v>286.08</v>
       </c>
       <c r="BF8" s="10" t="n">
-        <v>114.55</v>
+        <v>88.44</v>
       </c>
       <c r="BG8" s="10" t="inlineStr"/>
       <c r="BH8" s="10" t="inlineStr"/>
@@ -2059,17 +2079,17 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>534220111</t>
+          <t>534211757</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>46171.17877314815</v>
+        <v>46171.12677083333</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>46171.18686342592</v>
+        <v>46171.13321759259</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>4498.4</v>
+        <v>4501.1125</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
@@ -2077,26 +2097,26 @@
         </is>
       </c>
       <c r="H9" s="10" t="n">
-        <v>4499.02</v>
+        <v>4503.68</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>2.48</v>
+        <v>10.27</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.09</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>[sl 4498.95]</t>
+          <t>[sl 4501.22]</t>
         </is>
       </c>
       <c r="O9" s="10" t="inlineStr">
@@ -2154,10 +2174,10 @@
         </is>
       </c>
       <c r="BE9" s="10" t="n">
-        <v>617.4299999999999</v>
+        <v>542.55</v>
       </c>
       <c r="BF9" s="10" t="n">
-        <v>109.89</v>
+        <v>114.55</v>
       </c>
       <c r="BG9" s="10" t="inlineStr"/>
       <c r="BH9" s="10" t="inlineStr"/>
@@ -2178,44 +2198,44 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>534285946</t>
+          <t>534220111</t>
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>46171.40813657407</v>
+        <v>46171.17877314815</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>46171.45194444444</v>
+        <v>46171.18686342592</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4505.975</v>
+        <v>4498.4</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>4502.76</v>
+        <v>4499.02</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>12.86</v>
+        <v>2.48</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>3.58</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>6.93</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>[sl 4502.92]</t>
+          <t>[sl 4498.95]</t>
         </is>
       </c>
       <c r="O10" s="10" t="inlineStr">
@@ -2262,10 +2282,10 @@
       <c r="AZ10" s="10" t="inlineStr"/>
       <c r="BA10" s="10" t="inlineStr"/>
       <c r="BB10" s="11" t="n">
-        <v>46170.60416666666</v>
+        <v>46170.75</v>
       </c>
       <c r="BC10" s="10" t="n">
-        <v>4386.33</v>
+        <v>4389.13</v>
       </c>
       <c r="BD10" s="10" t="inlineStr">
         <is>
@@ -2273,10 +2293,10 @@
         </is>
       </c>
       <c r="BE10" s="10" t="n">
-        <v>1157.72</v>
+        <v>617.4299999999999</v>
       </c>
       <c r="BF10" s="10" t="n">
-        <v>116.43</v>
+        <v>109.89</v>
       </c>
       <c r="BG10" s="10" t="inlineStr"/>
       <c r="BH10" s="10" t="inlineStr"/>
@@ -2297,17 +2317,17 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>534387536</t>
+          <t>534285946</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>46171.56840277778</v>
+        <v>46171.40813657407</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>46171.63032407407</v>
+        <v>46171.45194444444</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4511.87</v>
+        <v>4505.975</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
@@ -2315,31 +2335,31 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>4504.96</v>
+        <v>4502.76</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>27.64</v>
+        <v>12.86</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>3.19</v>
+        <v>3.58</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>6.32</v>
+        <v>6.93</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>15.78</v>
+        <v>0.16</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>[sl 4520.74]</t>
+          <t>[sl 4502.92]</t>
         </is>
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15_M30]_S2</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr"/>
@@ -2392,10 +2412,10 @@
         </is>
       </c>
       <c r="BE11" s="10" t="n">
-        <v>1388.5</v>
+        <v>1157.72</v>
       </c>
       <c r="BF11" s="10" t="n">
-        <v>118.63</v>
+        <v>116.43</v>
       </c>
       <c r="BG11" s="10" t="inlineStr"/>
       <c r="BH11" s="10" t="inlineStr"/>
@@ -2411,54 +2431,54 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>NEAREST_ALREADY_MATCHED_OR_GREEDY</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>534640327</t>
+          <t>534387536</t>
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>46171.82914351852</v>
+        <v>46171.56840277778</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>46171.83998842593</v>
+        <v>46171.63032407407</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>4530.7775</v>
+        <v>4511.87</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H12" s="10" t="n">
-        <v>4534.9</v>
+        <v>4504.96</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>16.49</v>
+        <v>27.64</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>3.94</v>
+        <v>3.19</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>6.12</v>
+        <v>6.32</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>4.25</v>
+        <v>15.78</v>
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>[sl 4530.65]</t>
+          <t>[sl 4520.74]</t>
         </is>
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>[M5_M15_M30]_S2</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr"/>
@@ -2500,21 +2520,21 @@
       <c r="AZ12" s="10" t="inlineStr"/>
       <c r="BA12" s="10" t="inlineStr"/>
       <c r="BB12" s="11" t="n">
-        <v>46171.79166666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="BC12" s="10" t="n">
-        <v>4534.52</v>
+        <v>4386.33</v>
       </c>
       <c r="BD12" s="10" t="inlineStr">
         <is>
-          <t>SL_GUARD_CLOSE</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="BE12" s="10" t="n">
-        <v>53.97</v>
+        <v>1388.5</v>
       </c>
       <c r="BF12" s="10" t="n">
-        <v>0.38</v>
+        <v>118.63</v>
       </c>
       <c r="BG12" s="10" t="inlineStr"/>
       <c r="BH12" s="10" t="inlineStr"/>
@@ -2530,22 +2550,22 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:ENTRY_TOO_FAR</t>
+          <t>NEAREST_ALREADY_MATCHED_OR_GREEDY</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>534700993</t>
+          <t>534640327</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>46171.87479166667</v>
+        <v>46171.82914351852</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>46171.87481481482</v>
+        <v>46171.83998842593</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>4524.01</v>
+        <v>4530.7775</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
@@ -2553,31 +2573,31 @@
         </is>
       </c>
       <c r="H13" s="10" t="n">
-        <v>4523.73</v>
+        <v>4534.9</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>-1.12</v>
+        <v>16.49</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-0.28</v>
+        <v>2.18</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>-0.28</v>
+        <v>3.94</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-0.28</v>
+        <v>6.12</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-0.28</v>
+        <v>4.25</v>
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>[sl 4530.65]</t>
         </is>
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15_M30]_S2</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr"/>
@@ -2630,10 +2650,10 @@
         </is>
       </c>
       <c r="BE13" s="10" t="n">
-        <v>119.7</v>
+        <v>53.97</v>
       </c>
       <c r="BF13" s="10" t="n">
-        <v>10.79</v>
+        <v>0.38</v>
       </c>
       <c r="BG13" s="10" t="inlineStr"/>
       <c r="BH13" s="10" t="inlineStr"/>
@@ -2649,45 +2669,45 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>534919533</t>
+          <t>534700993</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>46171.98751157407</v>
+        <v>46171.87479166667</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>46171.9875462963</v>
+        <v>46171.87481481482</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>4565.07</v>
+        <v>4524.01</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H14" s="10" t="n">
-        <v>4563.77</v>
+        <v>4523.73</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>5.2</v>
+        <v>-1.12</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1.3</v>
+        <v>-0.28</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>1.3</v>
+        <v>-0.28</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>1.3</v>
+        <v>-0.28</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>1.3</v>
+        <v>-0.28</v>
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
@@ -2696,7 +2716,7 @@
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
-          <t>[M15_M30_H1]_S2</t>
+          <t>[M5_M15_M30]_S2</t>
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr"/>
@@ -2738,21 +2758,21 @@
       <c r="AZ14" s="10" t="inlineStr"/>
       <c r="BA14" s="10" t="inlineStr"/>
       <c r="BB14" s="11" t="n">
-        <v>46170.60416666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="BC14" s="10" t="n">
-        <v>4386.33</v>
+        <v>4534.52</v>
       </c>
       <c r="BD14" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="BE14" s="10" t="n">
-        <v>1992.02</v>
+        <v>119.7</v>
       </c>
       <c r="BF14" s="10" t="n">
-        <v>177.44</v>
+        <v>10.79</v>
       </c>
       <c r="BG14" s="10" t="inlineStr"/>
       <c r="BH14" s="10" t="inlineStr"/>
@@ -2768,22 +2788,22 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>534962292</t>
+          <t>534712433</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>46172.00015046296</v>
+        <v>46171.87508101852</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>46172.01085648148</v>
+        <v>46171.88037037037</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>4566.98</v>
+        <v>4521.0625</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
@@ -2791,31 +2811,31 @@
         </is>
       </c>
       <c r="H15" s="10" t="n">
-        <v>4571.73</v>
+        <v>4524.14</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>19</v>
+        <v>12.31</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>2.64</v>
+        <v>3.25</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>3.39</v>
+        <v>3.18</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>6.5</v>
+        <v>6.06</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>6.47</v>
+        <v>-0.18</v>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>[sl 4565.26]</t>
+          <t>[sl 4524.32]</t>
         </is>
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="P15" s="10" t="inlineStr"/>
@@ -2868,10 +2888,10 @@
         </is>
       </c>
       <c r="BE15" s="10" t="n">
-        <v>300.22</v>
+        <v>120.12</v>
       </c>
       <c r="BF15" s="10" t="n">
-        <v>37.21</v>
+        <v>10.38</v>
       </c>
       <c r="BG15" s="10" t="inlineStr"/>
       <c r="BH15" s="10" t="inlineStr"/>
@@ -2887,22 +2907,22 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>535341125</t>
+          <t>534919533</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>46174.56412037037</v>
+        <v>46171.98751157407</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>46174.570625</v>
+        <v>46171.9875462963</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>4519.092500000001</v>
+        <v>4565.07</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -2910,31 +2930,31 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>4515.68</v>
+        <v>4563.77</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>13.69</v>
+        <v>5.2</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>3.51</v>
+        <v>1.3</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>6.25</v>
+        <v>1.3</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>[sl 4517.42]</t>
+          <t>PD Zone fill che</t>
         </is>
       </c>
       <c r="O16" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>[M15_M30_H1]_S2</t>
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr"/>
@@ -2976,21 +2996,21 @@
       <c r="AZ16" s="10" t="inlineStr"/>
       <c r="BA16" s="10" t="inlineStr"/>
       <c r="BB16" s="11" t="n">
-        <v>46175.36458333334</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="BC16" s="10" t="n">
-        <v>4463.18</v>
+        <v>4386.33</v>
       </c>
       <c r="BD16" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="BE16" s="10" t="n">
-        <v>1152.67</v>
+        <v>1992.02</v>
       </c>
       <c r="BF16" s="10" t="n">
-        <v>52.5</v>
+        <v>177.44</v>
       </c>
       <c r="BG16" s="10" t="inlineStr"/>
       <c r="BH16" s="10" t="inlineStr"/>
@@ -3011,49 +3031,49 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>534365910</t>
+          <t>534962292</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>46174.61928240741</v>
+        <v>46172.00015046296</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>46174.62296296296</v>
+        <v>46172.01085648148</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>4501.66</v>
+        <v>4566.98</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H17" s="10" t="n">
-        <v>4501.15</v>
+        <v>4571.73</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>2.08</v>
+        <v>19</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.52</v>
+        <v>2.64</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>0.52</v>
+        <v>3.39</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>0.52</v>
+        <v>6.5</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>0.52</v>
+        <v>6.47</v>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>[sl 4501.66]</t>
+          <t>[sl 4565.26]</t>
         </is>
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr"/>
@@ -3095,21 +3115,21 @@
       <c r="AZ17" s="10" t="inlineStr"/>
       <c r="BA17" s="10" t="inlineStr"/>
       <c r="BB17" s="11" t="n">
-        <v>46175.36458333334</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="BC17" s="10" t="n">
-        <v>4463.18</v>
+        <v>4534.52</v>
       </c>
       <c r="BD17" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="BE17" s="10" t="n">
-        <v>1073.23</v>
+        <v>300.22</v>
       </c>
       <c r="BF17" s="10" t="n">
-        <v>37.97</v>
+        <v>37.21</v>
       </c>
       <c r="BG17" s="10" t="inlineStr"/>
       <c r="BH17" s="10" t="inlineStr"/>
@@ -3125,49 +3145,49 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>535430453</t>
+          <t>535341125</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>46174.66325231481</v>
+        <v>46174.56412037037</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>46174.66327546296</v>
+        <v>46174.570625</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>4496.13</v>
+        <v>4519.092500000001</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H18" s="10" t="n">
-        <v>4496.76</v>
+        <v>4515.68</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>3</v>
+        <v>13.69</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.75</v>
+        <v>2.18</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0.75</v>
+        <v>3.51</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>0.75</v>
+        <v>6.25</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>[sl 4517.42]</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
@@ -3214,21 +3234,21 @@
       <c r="AZ18" s="10" t="inlineStr"/>
       <c r="BA18" s="10" t="inlineStr"/>
       <c r="BB18" s="11" t="n">
-        <v>46174.41666666666</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="BC18" s="10" t="n">
-        <v>4525.13</v>
+        <v>4463.18</v>
       </c>
       <c r="BD18" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="BE18" s="10" t="n">
-        <v>355.08</v>
+        <v>1152.67</v>
       </c>
       <c r="BF18" s="10" t="n">
-        <v>28.37</v>
+        <v>52.5</v>
       </c>
       <c r="BG18" s="10" t="inlineStr"/>
       <c r="BH18" s="10" t="inlineStr"/>
@@ -3249,17 +3269,17 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>534621735</t>
+          <t>534365910</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>46174.88290509259</v>
+        <v>46174.61928240741</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>46175.01981481481</v>
+        <v>46174.62296296296</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>4467.2</v>
+        <v>4501.66</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
@@ -3267,31 +3287,31 @@
         </is>
       </c>
       <c r="H19" s="10" t="n">
-        <v>4489.03</v>
+        <v>4501.15</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>-86.64</v>
+        <v>2.08</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>-21.66</v>
+        <v>0.52</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>-21.66</v>
+        <v>0.52</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>-21.66</v>
+        <v>0.52</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>-21.66</v>
+        <v>0.52</v>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>MT5_CLOSE</t>
+          <t>[sl 4501.66]</t>
         </is>
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>[H1_H4_H12]_S2</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr"/>
@@ -3344,10 +3364,10 @@
         </is>
       </c>
       <c r="BE19" s="10" t="n">
-        <v>693.62</v>
+        <v>1073.23</v>
       </c>
       <c r="BF19" s="10" t="n">
-        <v>25.85</v>
+        <v>37.97</v>
       </c>
       <c r="BG19" s="10" t="inlineStr"/>
       <c r="BH19" s="10" t="inlineStr"/>
@@ -3368,40 +3388,40 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>536092728</t>
+          <t>535430453</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>46175.52091435185</v>
+        <v>46174.66325231481</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>46175.5209837963</v>
+        <v>46174.66327546296</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>4504.18</v>
+        <v>4496.13</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H20" s="10" t="n">
-        <v>4504.06</v>
+        <v>4496.76</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>1.52</v>
+        <v>3</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="M20" s="10" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
@@ -3410,7 +3430,7 @@
       </c>
       <c r="O20" s="10" t="inlineStr">
         <is>
-          <t>[M1_M5_M15]_S2</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="P20" s="10" t="inlineStr"/>
@@ -3452,21 +3472,21 @@
       <c r="AZ20" s="10" t="inlineStr"/>
       <c r="BA20" s="10" t="inlineStr"/>
       <c r="BB20" s="11" t="n">
-        <v>46175.36458333334</v>
+        <v>46174.41666666666</v>
       </c>
       <c r="BC20" s="10" t="n">
-        <v>4463.18</v>
+        <v>4525.13</v>
       </c>
       <c r="BD20" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="BE20" s="10" t="n">
-        <v>225.12</v>
+        <v>355.08</v>
       </c>
       <c r="BF20" s="10" t="n">
-        <v>40.88</v>
+        <v>28.37</v>
       </c>
       <c r="BG20" s="10" t="inlineStr"/>
       <c r="BH20" s="10" t="inlineStr"/>
@@ -3482,22 +3502,22 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>536096897</t>
+          <t>535530550</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>46175.52091435185</v>
+        <v>46174.79511574074</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>46175.5209837963</v>
+        <v>46174.8089699074</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>4504.18</v>
+        <v>4505.55</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
@@ -3505,31 +3525,31 @@
         </is>
       </c>
       <c r="H21" s="10" t="n">
-        <v>4503.99</v>
+        <v>4500.6</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1.52</v>
+        <v>20</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.38</v>
+        <v>2.25</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.38</v>
+        <v>3.08</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>0.38</v>
+        <v>6.14</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>0.38</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>[sl 4509.08]</t>
         </is>
       </c>
       <c r="O21" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr"/>
@@ -3582,10 +3602,10 @@
         </is>
       </c>
       <c r="BE21" s="10" t="n">
-        <v>225.12</v>
+        <v>820.03</v>
       </c>
       <c r="BF21" s="10" t="n">
-        <v>40.81</v>
+        <v>37.42</v>
       </c>
       <c r="BG21" s="10" t="inlineStr"/>
       <c r="BH21" s="10" t="inlineStr"/>
@@ -3606,17 +3626,17 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>536118248</t>
+          <t>536092728</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>46175.54528935185</v>
+        <v>46175.52091435185</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>46175.54528935185</v>
+        <v>46175.5209837963</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>4515.65</v>
+        <v>4504.18</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -3624,22 +3644,22 @@
         </is>
       </c>
       <c r="H22" s="10" t="n">
-        <v>4515.81</v>
+        <v>4504.06</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>-0.64</v>
+        <v>1.52</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.38</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.38</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.38</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.38</v>
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
@@ -3648,7 +3668,7 @@
       </c>
       <c r="O22" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>[M1_M5_M15]_S2</t>
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr"/>
@@ -3701,10 +3721,10 @@
         </is>
       </c>
       <c r="BE22" s="10" t="n">
-        <v>260.22</v>
+        <v>225.12</v>
       </c>
       <c r="BF22" s="10" t="n">
-        <v>52.63</v>
+        <v>40.88</v>
       </c>
       <c r="BG22" s="10" t="inlineStr"/>
       <c r="BH22" s="10" t="inlineStr"/>
@@ -3725,17 +3745,17 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>536140461</t>
+          <t>536096897</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>46175.5775</v>
+        <v>46175.52091435185</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>46175.57751157408</v>
+        <v>46175.5209837963</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>4519.67</v>
+        <v>4504.18</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
@@ -3743,22 +3763,22 @@
         </is>
       </c>
       <c r="H23" s="10" t="n">
-        <v>4519.72</v>
+        <v>4503.99</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0.16</v>
+        <v>1.52</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.04</v>
+        <v>0.38</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>0.04</v>
+        <v>0.38</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>0.04</v>
+        <v>0.38</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>0.04</v>
+        <v>0.38</v>
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
@@ -3767,7 +3787,7 @@
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="P23" s="10" t="inlineStr"/>
@@ -3820,10 +3840,10 @@
         </is>
       </c>
       <c r="BE23" s="10" t="n">
-        <v>306.6</v>
+        <v>225.12</v>
       </c>
       <c r="BF23" s="10" t="n">
-        <v>56.54</v>
+        <v>40.81</v>
       </c>
       <c r="BG23" s="10" t="inlineStr"/>
       <c r="BH23" s="10" t="inlineStr"/>
@@ -3844,17 +3864,17 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>536180512</t>
+          <t>536118248</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>46175.65538194445</v>
+        <v>46175.54528935185</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>46175.65540509259</v>
+        <v>46175.54528935185</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>4531.6</v>
+        <v>4515.65</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
@@ -3862,22 +3882,22 @@
         </is>
       </c>
       <c r="H24" s="10" t="n">
-        <v>4531.65</v>
+        <v>4515.81</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>0.16</v>
+        <v>-0.64</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="M24" s="10" t="n">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="N24" s="10" t="inlineStr">
         <is>
@@ -3886,7 +3906,7 @@
       </c>
       <c r="O24" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr"/>
@@ -3939,10 +3959,10 @@
         </is>
       </c>
       <c r="BE24" s="10" t="n">
-        <v>418.75</v>
+        <v>260.22</v>
       </c>
       <c r="BF24" s="10" t="n">
-        <v>68.47</v>
+        <v>52.63</v>
       </c>
       <c r="BG24" s="10" t="inlineStr"/>
       <c r="BH24" s="10" t="inlineStr"/>
@@ -3958,22 +3978,22 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>536129864</t>
+          <t>536140461</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>46175.87108796297</v>
+        <v>46175.5775</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>46175.875</v>
+        <v>46175.57751157408</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>4513.52</v>
+        <v>4519.67</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
@@ -3981,31 +4001,31 @@
         </is>
       </c>
       <c r="H25" s="10" t="n">
-        <v>4515.12</v>
+        <v>4519.72</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>-6.2</v>
+        <v>0.16</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>-1.55</v>
+        <v>0.04</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>-1.55</v>
+        <v>0.04</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>-1.55</v>
+        <v>0.04</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>-1.55</v>
+        <v>0.04</v>
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>#536129864 by #536052988</t>
+          <t>PD Zone fill che</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>[M5_M30_H1]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr"/>
@@ -4058,10 +4078,10 @@
         </is>
       </c>
       <c r="BE25" s="10" t="n">
-        <v>729.37</v>
+        <v>306.6</v>
       </c>
       <c r="BF25" s="10" t="n">
-        <v>51.94</v>
+        <v>56.54</v>
       </c>
       <c r="BG25" s="10" t="inlineStr"/>
       <c r="BH25" s="10" t="inlineStr"/>
@@ -4077,54 +4097,54 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>536634210</t>
+          <t>536180512</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>46176.42392361111</v>
+        <v>46175.65538194445</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>46176.42395833333</v>
+        <v>46175.65540509259</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>4479.58</v>
+        <v>4531.6</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>4479.44</v>
+        <v>4531.65</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.16</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="M26" s="10" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>Fill Trend Reche</t>
+          <t>PD Zone fill che</t>
         </is>
       </c>
       <c r="O26" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr"/>
@@ -4166,21 +4186,21 @@
       <c r="AZ26" s="10" t="inlineStr"/>
       <c r="BA26" s="10" t="inlineStr"/>
       <c r="BB26" s="11" t="n">
-        <v>46177.23958333334</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="BC26" s="10" t="n">
-        <v>4445.39</v>
+        <v>4463.18</v>
       </c>
       <c r="BD26" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="BE26" s="10" t="n">
-        <v>1174.55</v>
+        <v>418.75</v>
       </c>
       <c r="BF26" s="10" t="n">
-        <v>34.05</v>
+        <v>68.47</v>
       </c>
       <c r="BG26" s="10" t="inlineStr"/>
       <c r="BH26" s="10" t="inlineStr"/>
@@ -4196,22 +4216,22 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>537233013</t>
+          <t>536611496</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>46177.17019675926</v>
+        <v>46176.37560185185</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>46177.18942129629</v>
+        <v>46176.37864583333</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>4436.19</v>
+        <v>4472.38</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
@@ -4219,22 +4239,22 @@
         </is>
       </c>
       <c r="H27" s="10" t="n">
-        <v>4441.21</v>
+        <v>4481.32</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>-18.32</v>
+        <v>-34.68</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>-4.58</v>
+        <v>-8.67</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>-4.58</v>
+        <v>-8.67</v>
       </c>
       <c r="L27" s="10" t="n">
-        <v>-4.58</v>
+        <v>-8.67</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>-4.58</v>
+        <v>-8.67</v>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
@@ -4243,7 +4263,7 @@
       </c>
       <c r="O27" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15_M30]_S2</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr"/>
@@ -4285,21 +4305,21 @@
       <c r="AZ27" s="10" t="inlineStr"/>
       <c r="BA27" s="10" t="inlineStr"/>
       <c r="BB27" s="11" t="n">
-        <v>46178.42708333334</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="BC27" s="10" t="n">
-        <v>4436.72</v>
+        <v>4463.18</v>
       </c>
       <c r="BD27" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="BE27" s="10" t="n">
-        <v>1809.92</v>
+        <v>1455.87</v>
       </c>
       <c r="BF27" s="10" t="n">
-        <v>4.49</v>
+        <v>18.14</v>
       </c>
       <c r="BG27" s="10" t="inlineStr"/>
       <c r="BH27" s="10" t="inlineStr"/>
@@ -4315,54 +4335,54 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>537277914</t>
+          <t>536634210</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>46177.34267361111</v>
+        <v>46176.42392361111</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>46177.34271990741</v>
+        <v>46176.42395833333</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>4454.16</v>
+        <v>4479.58</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>4453.59</v>
+        <v>4479.44</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>2.56</v>
+        <v>-0.16</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.64</v>
+        <v>-0.04</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0.64</v>
+        <v>-0.04</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>0.64</v>
+        <v>-0.04</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>0.64</v>
+        <v>-0.04</v>
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>Fill Trend Reche</t>
         </is>
       </c>
       <c r="O28" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr"/>
@@ -4404,10 +4424,10 @@
       <c r="AZ28" s="10" t="inlineStr"/>
       <c r="BA28" s="10" t="inlineStr"/>
       <c r="BB28" s="11" t="n">
-        <v>46178.42708333334</v>
+        <v>46177.23958333334</v>
       </c>
       <c r="BC28" s="10" t="n">
-        <v>4436.72</v>
+        <v>4445.39</v>
       </c>
       <c r="BD28" s="10" t="inlineStr">
         <is>
@@ -4415,10 +4435,10 @@
         </is>
       </c>
       <c r="BE28" s="10" t="n">
-        <v>1561.55</v>
+        <v>1174.55</v>
       </c>
       <c r="BF28" s="10" t="n">
-        <v>16.87</v>
+        <v>34.05</v>
       </c>
       <c r="BG28" s="10" t="inlineStr"/>
       <c r="BH28" s="10" t="inlineStr"/>
@@ -4434,54 +4454,54 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>537984794</t>
+          <t>537233013</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>46178.35443287037</v>
+        <v>46177.17019675926</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>46178.35444444444</v>
+        <v>46177.18942129629</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>4457.81</v>
+        <v>4436.19</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>4457.7</v>
+        <v>4441.21</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>0.72</v>
+        <v>-18.32</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.18</v>
+        <v>-4.58</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0.18</v>
+        <v>-4.58</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>0.18</v>
+        <v>-4.58</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>0.18</v>
+        <v>-4.58</v>
       </c>
       <c r="N29" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>SL Guard Group a</t>
         </is>
       </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>[M5_M15_M30]_S2</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr"/>
@@ -4523,10 +4543,10 @@
       <c r="AZ29" s="10" t="inlineStr"/>
       <c r="BA29" s="10" t="inlineStr"/>
       <c r="BB29" s="11" t="n">
-        <v>46177.23958333334</v>
+        <v>46178.42708333334</v>
       </c>
       <c r="BC29" s="10" t="n">
-        <v>4445.39</v>
+        <v>4436.72</v>
       </c>
       <c r="BD29" s="10" t="inlineStr">
         <is>
@@ -4534,10 +4554,10 @@
         </is>
       </c>
       <c r="BE29" s="10" t="n">
-        <v>1605.38</v>
+        <v>1809.92</v>
       </c>
       <c r="BF29" s="10" t="n">
-        <v>12.31</v>
+        <v>4.49</v>
       </c>
       <c r="BG29" s="10" t="inlineStr"/>
       <c r="BH29" s="10" t="inlineStr"/>
@@ -4558,40 +4578,40 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>537975016</t>
+          <t>537277914</t>
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>46178.35872685185</v>
+        <v>46177.34267361111</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>46178.35872685185</v>
+        <v>46177.34271990741</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4466.56</v>
+        <v>4454.16</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>4466.12</v>
+        <v>4453.59</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>-0.64</v>
+        <v>2.56</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.64</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.64</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.64</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.64</v>
       </c>
       <c r="N30" s="10" t="inlineStr">
         <is>
@@ -4600,7 +4620,7 @@
       </c>
       <c r="O30" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr"/>
@@ -4642,10 +4662,10 @@
       <c r="AZ30" s="10" t="inlineStr"/>
       <c r="BA30" s="10" t="inlineStr"/>
       <c r="BB30" s="11" t="n">
-        <v>46177.23958333334</v>
+        <v>46178.42708333334</v>
       </c>
       <c r="BC30" s="10" t="n">
-        <v>4445.39</v>
+        <v>4436.72</v>
       </c>
       <c r="BD30" s="10" t="inlineStr">
         <is>
@@ -4653,10 +4673,10 @@
         </is>
       </c>
       <c r="BE30" s="10" t="n">
-        <v>1611.57</v>
+        <v>1561.55</v>
       </c>
       <c r="BF30" s="10" t="n">
-        <v>20.73</v>
+        <v>16.87</v>
       </c>
       <c r="BG30" s="10" t="inlineStr"/>
       <c r="BH30" s="10" t="inlineStr"/>
@@ -4667,27 +4687,61 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>BACKTEST_ONLY</t>
+          <t>LIVE_ONLY</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr"/>
-      <c r="D31" s="10" t="inlineStr"/>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="10" t="inlineStr"/>
-      <c r="G31" s="10" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-      <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="10" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" s="10" t="inlineStr"/>
-      <c r="O31" s="10" t="inlineStr"/>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>537416021</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>46177.5493287037</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>46177.54938657407</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>4472.07</v>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>4472.82</v>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L31" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>PD Zone fill che</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>[M15_M30]_S2</t>
+        </is>
+      </c>
       <c r="P31" s="10" t="inlineStr"/>
       <c r="Q31" s="10" t="inlineStr"/>
       <c r="R31" s="10" t="inlineStr"/>
@@ -4702,35 +4756,17 @@
       <c r="AA31" s="10" t="inlineStr"/>
       <c r="AB31" s="10" t="inlineStr"/>
       <c r="AC31" s="10" t="inlineStr"/>
-      <c r="AD31" s="11" t="n">
-        <v>46170.60416666666</v>
-      </c>
-      <c r="AE31" s="11" t="n">
-        <v>46170.75</v>
-      </c>
-      <c r="AF31" s="10" t="n">
-        <v>4386.47</v>
-      </c>
-      <c r="AG31" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH31" s="10" t="n">
-        <v>4386.33</v>
-      </c>
-      <c r="AI31" s="10" t="n">
-        <v>0.14</v>
-      </c>
+      <c r="AD31" s="10" t="inlineStr"/>
+      <c r="AE31" s="10" t="inlineStr"/>
+      <c r="AF31" s="10" t="inlineStr"/>
+      <c r="AG31" s="10" t="inlineStr"/>
+      <c r="AH31" s="10" t="inlineStr"/>
+      <c r="AI31" s="10" t="inlineStr"/>
       <c r="AJ31" s="10" t="inlineStr"/>
       <c r="AK31" s="10" t="inlineStr"/>
       <c r="AL31" s="10" t="inlineStr"/>
       <c r="AM31" s="10" t="inlineStr"/>
-      <c r="AN31" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
+      <c r="AN31" s="10" t="inlineStr"/>
       <c r="AO31" s="10" t="inlineStr"/>
       <c r="AP31" s="10" t="inlineStr"/>
       <c r="AQ31" s="10" t="inlineStr"/>
@@ -4744,53 +4780,87 @@
       <c r="AY31" s="10" t="inlineStr"/>
       <c r="AZ31" s="10" t="inlineStr"/>
       <c r="BA31" s="10" t="inlineStr"/>
-      <c r="BB31" s="10" t="inlineStr"/>
-      <c r="BC31" s="10" t="inlineStr"/>
-      <c r="BD31" s="10" t="inlineStr"/>
-      <c r="BE31" s="10" t="inlineStr"/>
-      <c r="BF31" s="10" t="inlineStr"/>
-      <c r="BG31" s="11" t="n">
-        <v>46171.40813657407</v>
-      </c>
-      <c r="BH31" s="10" t="n">
-        <v>4502.76</v>
-      </c>
-      <c r="BI31" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4502.92]</t>
-        </is>
-      </c>
-      <c r="BJ31" s="10" t="n">
-        <v>1157.72</v>
-      </c>
-      <c r="BK31" s="10" t="n">
-        <v>116.43</v>
-      </c>
+      <c r="BB31" s="11" t="n">
+        <v>46178.42708333334</v>
+      </c>
+      <c r="BC31" s="10" t="n">
+        <v>4436.72</v>
+      </c>
+      <c r="BD31" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="BE31" s="10" t="n">
+        <v>1263.97</v>
+      </c>
+      <c r="BF31" s="10" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="BG31" s="10" t="inlineStr"/>
+      <c r="BH31" s="10" t="inlineStr"/>
+      <c r="BI31" s="10" t="inlineStr"/>
+      <c r="BJ31" s="10" t="inlineStr"/>
+      <c r="BK31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>BACKTEST_ONLY</t>
+          <t>LIVE_ONLY</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr"/>
-      <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="10" t="inlineStr"/>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="10" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
-      <c r="K32" s="10" t="inlineStr"/>
-      <c r="L32" s="10" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" s="10" t="inlineStr"/>
-      <c r="O32" s="10" t="inlineStr"/>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>537984794</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>46178.35443287037</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>46178.35444444444</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>4457.81</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>4457.7</v>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M32" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>PD Zone fill che</t>
+        </is>
+      </c>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>M15_S2_P2</t>
+        </is>
+      </c>
       <c r="P32" s="10" t="inlineStr"/>
       <c r="Q32" s="10" t="inlineStr"/>
       <c r="R32" s="10" t="inlineStr"/>
@@ -4805,107 +4875,111 @@
       <c r="AA32" s="10" t="inlineStr"/>
       <c r="AB32" s="10" t="inlineStr"/>
       <c r="AC32" s="10" t="inlineStr"/>
-      <c r="AD32" s="11" t="n">
-        <v>46174.41666666666</v>
-      </c>
-      <c r="AE32" s="11" t="n">
-        <v>46174.5</v>
-      </c>
-      <c r="AF32" s="10" t="n">
-        <v>4515.69</v>
-      </c>
-      <c r="AG32" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH32" s="10" t="n">
-        <v>4525.13</v>
-      </c>
-      <c r="AI32" s="10" t="n">
-        <v>9.44</v>
-      </c>
+      <c r="AD32" s="10" t="inlineStr"/>
+      <c r="AE32" s="10" t="inlineStr"/>
+      <c r="AF32" s="10" t="inlineStr"/>
+      <c r="AG32" s="10" t="inlineStr"/>
+      <c r="AH32" s="10" t="inlineStr"/>
+      <c r="AI32" s="10" t="inlineStr"/>
       <c r="AJ32" s="10" t="inlineStr"/>
       <c r="AK32" s="10" t="inlineStr"/>
       <c r="AL32" s="10" t="inlineStr"/>
       <c r="AM32" s="10" t="inlineStr"/>
-      <c r="AN32" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
+      <c r="AN32" s="10" t="inlineStr"/>
       <c r="AO32" s="10" t="inlineStr"/>
       <c r="AP32" s="10" t="inlineStr"/>
       <c r="AQ32" s="10" t="inlineStr"/>
       <c r="AR32" s="10" t="inlineStr"/>
       <c r="AS32" s="10" t="inlineStr"/>
       <c r="AT32" s="10" t="inlineStr"/>
-      <c r="AU32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV32" s="10" t="n"/>
-      <c r="AW32" s="10" t="n">
-        <v>4515.69</v>
-      </c>
-      <c r="AX32" s="10" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="AY32" s="10" t="inlineStr">
-        <is>
-          <t>M5 4515.69</t>
-        </is>
-      </c>
+      <c r="AU32" s="10" t="inlineStr"/>
+      <c r="AV32" s="10" t="inlineStr"/>
+      <c r="AW32" s="10" t="inlineStr"/>
+      <c r="AX32" s="10" t="inlineStr"/>
+      <c r="AY32" s="10" t="inlineStr"/>
       <c r="AZ32" s="10" t="inlineStr"/>
       <c r="BA32" s="10" t="inlineStr"/>
-      <c r="BB32" s="10" t="inlineStr"/>
-      <c r="BC32" s="10" t="inlineStr"/>
-      <c r="BD32" s="10" t="inlineStr"/>
-      <c r="BE32" s="10" t="inlineStr"/>
-      <c r="BF32" s="10" t="inlineStr"/>
-      <c r="BG32" s="11" t="n">
-        <v>46174.66325231481</v>
-      </c>
-      <c r="BH32" s="10" t="n">
-        <v>4496.76</v>
-      </c>
-      <c r="BI32" s="10" t="inlineStr">
-        <is>
-          <t>PD Zone fill che</t>
-        </is>
-      </c>
-      <c r="BJ32" s="10" t="n">
-        <v>355.08</v>
-      </c>
-      <c r="BK32" s="10" t="n">
-        <v>28.37</v>
-      </c>
+      <c r="BB32" s="11" t="n">
+        <v>46177.23958333334</v>
+      </c>
+      <c r="BC32" s="10" t="n">
+        <v>4445.39</v>
+      </c>
+      <c r="BD32" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="BE32" s="10" t="n">
+        <v>1605.38</v>
+      </c>
+      <c r="BF32" s="10" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="BG32" s="10" t="inlineStr"/>
+      <c r="BH32" s="10" t="inlineStr"/>
+      <c r="BI32" s="10" t="inlineStr"/>
+      <c r="BJ32" s="10" t="inlineStr"/>
+      <c r="BK32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>BACKTEST_ONLY</t>
+          <t>LIVE_ONLY</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr"/>
-      <c r="D33" s="10" t="inlineStr"/>
-      <c r="E33" s="10" t="inlineStr"/>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="10" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr"/>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
-      <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="10" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" s="10" t="inlineStr"/>
-      <c r="O33" s="10" t="inlineStr"/>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>537975016</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>46178.35872685185</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>46178.35872685185</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>4466.56</v>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>4466.12</v>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L33" s="10" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>PD Zone fill che</t>
+        </is>
+      </c>
+      <c r="O33" s="10" t="inlineStr">
+        <is>
+          <t>M15_S2_P1</t>
+        </is>
+      </c>
       <c r="P33" s="10" t="inlineStr"/>
       <c r="Q33" s="10" t="inlineStr"/>
       <c r="R33" s="10" t="inlineStr"/>
@@ -4920,35 +4994,17 @@
       <c r="AA33" s="10" t="inlineStr"/>
       <c r="AB33" s="10" t="inlineStr"/>
       <c r="AC33" s="10" t="inlineStr"/>
-      <c r="AD33" s="11" t="n">
-        <v>46175.36458333334</v>
-      </c>
-      <c r="AE33" s="11" t="n">
-        <v>46175.45833333334</v>
-      </c>
-      <c r="AF33" s="10" t="n">
-        <v>4502.48</v>
-      </c>
-      <c r="AG33" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH33" s="10" t="n">
-        <v>4463.18</v>
-      </c>
-      <c r="AI33" s="10" t="n">
-        <v>39.3</v>
-      </c>
+      <c r="AD33" s="10" t="inlineStr"/>
+      <c r="AE33" s="10" t="inlineStr"/>
+      <c r="AF33" s="10" t="inlineStr"/>
+      <c r="AG33" s="10" t="inlineStr"/>
+      <c r="AH33" s="10" t="inlineStr"/>
+      <c r="AI33" s="10" t="inlineStr"/>
       <c r="AJ33" s="10" t="inlineStr"/>
       <c r="AK33" s="10" t="inlineStr"/>
       <c r="AL33" s="10" t="inlineStr"/>
       <c r="AM33" s="10" t="inlineStr"/>
-      <c r="AN33" s="10" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
+      <c r="AN33" s="10" t="inlineStr"/>
       <c r="AO33" s="10" t="inlineStr"/>
       <c r="AP33" s="10" t="inlineStr"/>
       <c r="AQ33" s="10" t="inlineStr"/>
@@ -4962,28 +5018,28 @@
       <c r="AY33" s="10" t="inlineStr"/>
       <c r="AZ33" s="10" t="inlineStr"/>
       <c r="BA33" s="10" t="inlineStr"/>
-      <c r="BB33" s="10" t="inlineStr"/>
-      <c r="BC33" s="10" t="inlineStr"/>
-      <c r="BD33" s="10" t="inlineStr"/>
-      <c r="BE33" s="10" t="inlineStr"/>
-      <c r="BF33" s="10" t="inlineStr"/>
-      <c r="BG33" s="11" t="n">
-        <v>46175.52091435185</v>
-      </c>
-      <c r="BH33" s="10" t="n">
-        <v>4503.99</v>
-      </c>
-      <c r="BI33" s="10" t="inlineStr">
-        <is>
-          <t>PD Zone fill che</t>
-        </is>
-      </c>
-      <c r="BJ33" s="10" t="n">
-        <v>225.12</v>
-      </c>
-      <c r="BK33" s="10" t="n">
-        <v>40.81</v>
-      </c>
+      <c r="BB33" s="11" t="n">
+        <v>46177.23958333334</v>
+      </c>
+      <c r="BC33" s="10" t="n">
+        <v>4445.39</v>
+      </c>
+      <c r="BD33" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="BE33" s="10" t="n">
+        <v>1611.57</v>
+      </c>
+      <c r="BF33" s="10" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="BG33" s="10" t="inlineStr"/>
+      <c r="BH33" s="10" t="inlineStr"/>
+      <c r="BI33" s="10" t="inlineStr"/>
+      <c r="BJ33" s="10" t="inlineStr"/>
+      <c r="BK33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -5024,13 +5080,13 @@
       <c r="AB34" s="10" t="inlineStr"/>
       <c r="AC34" s="10" t="inlineStr"/>
       <c r="AD34" s="11" t="n">
-        <v>46177.23958333334</v>
+        <v>46174.41666666666</v>
       </c>
       <c r="AE34" s="11" t="n">
-        <v>46177.28125</v>
+        <v>46174.5</v>
       </c>
       <c r="AF34" s="10" t="n">
-        <v>4461.57</v>
+        <v>4515.69</v>
       </c>
       <c r="AG34" s="10" t="inlineStr">
         <is>
@@ -5038,10 +5094,10 @@
         </is>
       </c>
       <c r="AH34" s="10" t="n">
-        <v>4445.39</v>
+        <v>4525.13</v>
       </c>
       <c r="AI34" s="10" t="n">
-        <v>-16.18</v>
+        <v>9.44</v>
       </c>
       <c r="AJ34" s="10" t="inlineStr"/>
       <c r="AK34" s="10" t="inlineStr"/>
@@ -5058,11 +5114,23 @@
       <c r="AR34" s="10" t="inlineStr"/>
       <c r="AS34" s="10" t="inlineStr"/>
       <c r="AT34" s="10" t="inlineStr"/>
-      <c r="AU34" s="10" t="inlineStr"/>
-      <c r="AV34" s="10" t="inlineStr"/>
-      <c r="AW34" s="10" t="inlineStr"/>
-      <c r="AX34" s="10" t="inlineStr"/>
-      <c r="AY34" s="10" t="inlineStr"/>
+      <c r="AU34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV34" s="10" t="n"/>
+      <c r="AW34" s="10" t="n">
+        <v>4515.69</v>
+      </c>
+      <c r="AX34" s="10" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="AY34" s="10" t="inlineStr">
+        <is>
+          <t>M5 4515.69</t>
+        </is>
+      </c>
       <c r="AZ34" s="10" t="inlineStr"/>
       <c r="BA34" s="10" t="inlineStr"/>
       <c r="BB34" s="10" t="inlineStr"/>
@@ -5071,21 +5139,21 @@
       <c r="BE34" s="10" t="inlineStr"/>
       <c r="BF34" s="10" t="inlineStr"/>
       <c r="BG34" s="11" t="n">
-        <v>46176.42392361111</v>
+        <v>46174.66325231481</v>
       </c>
       <c r="BH34" s="10" t="n">
-        <v>4479.44</v>
+        <v>4496.76</v>
       </c>
       <c r="BI34" s="10" t="inlineStr">
         <is>
-          <t>Fill Trend Reche</t>
+          <t>PD Zone fill che</t>
         </is>
       </c>
       <c r="BJ34" s="10" t="n">
-        <v>1174.55</v>
+        <v>355.08</v>
       </c>
       <c r="BK34" s="10" t="n">
-        <v>34.05</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="35">
@@ -5127,13 +5195,13 @@
       <c r="AB35" s="10" t="inlineStr"/>
       <c r="AC35" s="10" t="inlineStr"/>
       <c r="AD35" s="11" t="n">
-        <v>46178.42708333334</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="AE35" s="11" t="n">
-        <v>46178.52083333334</v>
+        <v>46175.45833333334</v>
       </c>
       <c r="AF35" s="10" t="n">
-        <v>4439.68</v>
+        <v>4502.48</v>
       </c>
       <c r="AG35" s="10" t="inlineStr">
         <is>
@@ -5141,10 +5209,10 @@
         </is>
       </c>
       <c r="AH35" s="10" t="n">
-        <v>4436.72</v>
+        <v>4463.18</v>
       </c>
       <c r="AI35" s="10" t="n">
-        <v>2.96</v>
+        <v>39.3</v>
       </c>
       <c r="AJ35" s="10" t="inlineStr"/>
       <c r="AK35" s="10" t="inlineStr"/>
@@ -5152,7 +5220,7 @@
       <c r="AM35" s="10" t="inlineStr"/>
       <c r="AN35" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO35" s="10" t="inlineStr"/>
@@ -5161,23 +5229,11 @@
       <c r="AR35" s="10" t="inlineStr"/>
       <c r="AS35" s="10" t="inlineStr"/>
       <c r="AT35" s="10" t="inlineStr"/>
-      <c r="AU35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV35" s="10" t="n"/>
-      <c r="AW35" s="10" t="n">
-        <v>4439.68</v>
-      </c>
-      <c r="AX35" s="10" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="AY35" s="10" t="inlineStr">
-        <is>
-          <t>M5 4439.68</t>
-        </is>
-      </c>
+      <c r="AU35" s="10" t="inlineStr"/>
+      <c r="AV35" s="10" t="inlineStr"/>
+      <c r="AW35" s="10" t="inlineStr"/>
+      <c r="AX35" s="10" t="inlineStr"/>
+      <c r="AY35" s="10" t="inlineStr"/>
       <c r="AZ35" s="10" t="inlineStr"/>
       <c r="BA35" s="10" t="inlineStr"/>
       <c r="BB35" s="10" t="inlineStr"/>
@@ -5186,10 +5242,10 @@
       <c r="BE35" s="10" t="inlineStr"/>
       <c r="BF35" s="10" t="inlineStr"/>
       <c r="BG35" s="11" t="n">
-        <v>46177.34267361111</v>
+        <v>46175.52091435185</v>
       </c>
       <c r="BH35" s="10" t="n">
-        <v>4453.59</v>
+        <v>4503.99</v>
       </c>
       <c r="BI35" s="10" t="inlineStr">
         <is>
@@ -5197,14 +5253,232 @@
         </is>
       </c>
       <c r="BJ35" s="10" t="n">
-        <v>1561.55</v>
+        <v>225.12</v>
       </c>
       <c r="BK35" s="10" t="n">
-        <v>16.87</v>
+        <v>40.81</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr"/>
+      <c r="D36" s="10" t="inlineStr"/>
+      <c r="E36" s="10" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr"/>
+      <c r="G36" s="10" t="inlineStr"/>
+      <c r="H36" s="10" t="inlineStr"/>
+      <c r="I36" s="10" t="inlineStr"/>
+      <c r="J36" s="10" t="inlineStr"/>
+      <c r="K36" s="10" t="inlineStr"/>
+      <c r="L36" s="10" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
+      <c r="O36" s="10" t="inlineStr"/>
+      <c r="P36" s="10" t="inlineStr"/>
+      <c r="Q36" s="10" t="inlineStr"/>
+      <c r="R36" s="10" t="inlineStr"/>
+      <c r="S36" s="10" t="inlineStr"/>
+      <c r="T36" s="10" t="inlineStr"/>
+      <c r="U36" s="10" t="inlineStr"/>
+      <c r="V36" s="10" t="inlineStr"/>
+      <c r="W36" s="10" t="inlineStr"/>
+      <c r="X36" s="10" t="inlineStr"/>
+      <c r="Y36" s="10" t="inlineStr"/>
+      <c r="Z36" s="10" t="inlineStr"/>
+      <c r="AA36" s="10" t="inlineStr"/>
+      <c r="AB36" s="10" t="inlineStr"/>
+      <c r="AC36" s="10" t="inlineStr"/>
+      <c r="AD36" s="11" t="n">
+        <v>46177.23958333334</v>
+      </c>
+      <c r="AE36" s="11" t="n">
+        <v>46177.28125</v>
+      </c>
+      <c r="AF36" s="10" t="n">
+        <v>4461.57</v>
+      </c>
+      <c r="AG36" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="AH36" s="10" t="n">
+        <v>4445.39</v>
+      </c>
+      <c r="AI36" s="10" t="n">
+        <v>-16.18</v>
+      </c>
+      <c r="AJ36" s="10" t="inlineStr"/>
+      <c r="AK36" s="10" t="inlineStr"/>
+      <c r="AL36" s="10" t="inlineStr"/>
+      <c r="AM36" s="10" t="inlineStr"/>
+      <c r="AN36" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO36" s="10" t="inlineStr"/>
+      <c r="AP36" s="10" t="inlineStr"/>
+      <c r="AQ36" s="10" t="inlineStr"/>
+      <c r="AR36" s="10" t="inlineStr"/>
+      <c r="AS36" s="10" t="inlineStr"/>
+      <c r="AT36" s="10" t="inlineStr"/>
+      <c r="AU36" s="10" t="inlineStr"/>
+      <c r="AV36" s="10" t="inlineStr"/>
+      <c r="AW36" s="10" t="inlineStr"/>
+      <c r="AX36" s="10" t="inlineStr"/>
+      <c r="AY36" s="10" t="inlineStr"/>
+      <c r="AZ36" s="10" t="inlineStr"/>
+      <c r="BA36" s="10" t="inlineStr"/>
+      <c r="BB36" s="10" t="inlineStr"/>
+      <c r="BC36" s="10" t="inlineStr"/>
+      <c r="BD36" s="10" t="inlineStr"/>
+      <c r="BE36" s="10" t="inlineStr"/>
+      <c r="BF36" s="10" t="inlineStr"/>
+      <c r="BG36" s="11" t="n">
+        <v>46176.42392361111</v>
+      </c>
+      <c r="BH36" s="10" t="n">
+        <v>4479.44</v>
+      </c>
+      <c r="BI36" s="10" t="inlineStr">
+        <is>
+          <t>Fill Trend Reche</t>
+        </is>
+      </c>
+      <c r="BJ36" s="10" t="n">
+        <v>1174.55</v>
+      </c>
+      <c r="BK36" s="10" t="n">
+        <v>34.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr"/>
+      <c r="D37" s="10" t="inlineStr"/>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr"/>
+      <c r="G37" s="10" t="inlineStr"/>
+      <c r="H37" s="10" t="inlineStr"/>
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" s="10" t="inlineStr"/>
+      <c r="K37" s="10" t="inlineStr"/>
+      <c r="L37" s="10" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
+      <c r="O37" s="10" t="inlineStr"/>
+      <c r="P37" s="10" t="inlineStr"/>
+      <c r="Q37" s="10" t="inlineStr"/>
+      <c r="R37" s="10" t="inlineStr"/>
+      <c r="S37" s="10" t="inlineStr"/>
+      <c r="T37" s="10" t="inlineStr"/>
+      <c r="U37" s="10" t="inlineStr"/>
+      <c r="V37" s="10" t="inlineStr"/>
+      <c r="W37" s="10" t="inlineStr"/>
+      <c r="X37" s="10" t="inlineStr"/>
+      <c r="Y37" s="10" t="inlineStr"/>
+      <c r="Z37" s="10" t="inlineStr"/>
+      <c r="AA37" s="10" t="inlineStr"/>
+      <c r="AB37" s="10" t="inlineStr"/>
+      <c r="AC37" s="10" t="inlineStr"/>
+      <c r="AD37" s="11" t="n">
+        <v>46178.42708333334</v>
+      </c>
+      <c r="AE37" s="11" t="n">
+        <v>46178.52083333334</v>
+      </c>
+      <c r="AF37" s="10" t="n">
+        <v>4439.68</v>
+      </c>
+      <c r="AG37" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH37" s="10" t="n">
+        <v>4436.72</v>
+      </c>
+      <c r="AI37" s="10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AJ37" s="10" t="inlineStr"/>
+      <c r="AK37" s="10" t="inlineStr"/>
+      <c r="AL37" s="10" t="inlineStr"/>
+      <c r="AM37" s="10" t="inlineStr"/>
+      <c r="AN37" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO37" s="10" t="inlineStr"/>
+      <c r="AP37" s="10" t="inlineStr"/>
+      <c r="AQ37" s="10" t="inlineStr"/>
+      <c r="AR37" s="10" t="inlineStr"/>
+      <c r="AS37" s="10" t="inlineStr"/>
+      <c r="AT37" s="10" t="inlineStr"/>
+      <c r="AU37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV37" s="10" t="n"/>
+      <c r="AW37" s="10" t="n">
+        <v>4439.68</v>
+      </c>
+      <c r="AX37" s="10" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="AY37" s="10" t="inlineStr">
+        <is>
+          <t>M5 4439.68</t>
+        </is>
+      </c>
+      <c r="AZ37" s="10" t="inlineStr"/>
+      <c r="BA37" s="10" t="inlineStr"/>
+      <c r="BB37" s="10" t="inlineStr"/>
+      <c r="BC37" s="10" t="inlineStr"/>
+      <c r="BD37" s="10" t="inlineStr"/>
+      <c r="BE37" s="10" t="inlineStr"/>
+      <c r="BF37" s="10" t="inlineStr"/>
+      <c r="BG37" s="11" t="n">
+        <v>46177.5493287037</v>
+      </c>
+      <c r="BH37" s="10" t="n">
+        <v>4472.82</v>
+      </c>
+      <c r="BI37" s="10" t="inlineStr">
+        <is>
+          <t>PD Zone fill che</t>
+        </is>
+      </c>
+      <c r="BJ37" s="10" t="n">
+        <v>1263.97</v>
+      </c>
+      <c r="BK37" s="10" t="n">
+        <v>36.1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BK35"/>
+  <autoFilter ref="A1:BK37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5215,7 +5489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK3"/>
+  <dimension ref="A1:BK4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5608,54 +5882,54 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>LOOSE_MATCH_SL_GUARD</t>
+          <t>PNL_DIFF_SAME_BUCKET</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>534643103</t>
+          <t>533469126</t>
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>46171.82914351852</v>
+        <v>46170.58363425926</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>46171.83998842593</v>
+        <v>46170.58751157407</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>4530.5775</v>
+        <v>4385.14</v>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H2" s="8" t="n">
-        <v>4534.57</v>
+        <v>4387.4</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>15.97</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>2.38</v>
+        <v>-2.26</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>3.62</v>
+        <v>-2.26</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>6.05</v>
+        <v>-2.26</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>3.92</v>
+        <v>-2.26</v>
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>[sl 4530.65]</t>
+          <t>[sl 4385.14]</t>
         </is>
       </c>
       <c r="O2" s="8" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="P2" s="8" t="inlineStr"/>
@@ -5673,24 +5947,24 @@
       <c r="AB2" s="8" t="inlineStr"/>
       <c r="AC2" s="8" t="inlineStr"/>
       <c r="AD2" s="9" t="n">
-        <v>46171.79166666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="AE2" s="9" t="n">
-        <v>46171.89583333334</v>
+        <v>46170.75</v>
       </c>
       <c r="AF2" s="8" t="n">
-        <v>4564.21</v>
+        <v>4386.49</v>
       </c>
       <c r="AG2" s="8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH2" s="8" t="n">
-        <v>4534.52</v>
+        <v>4386.33</v>
       </c>
       <c r="AI2" s="8" t="n">
-        <v>-29.69</v>
+        <v>0.16</v>
       </c>
       <c r="AJ2" s="8" t="inlineStr"/>
       <c r="AK2" s="8" t="inlineStr"/>
@@ -5698,28 +5972,28 @@
       <c r="AM2" s="8" t="inlineStr"/>
       <c r="AN2" s="8" t="inlineStr">
         <is>
-          <t>SL_GUARD_CLOSE</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO2" s="8" t="inlineStr">
         <is>
-          <t>LOOSE</t>
+          <t>NEAR</t>
         </is>
       </c>
       <c r="AP2" s="8" t="n">
-        <v>539.72</v>
+        <v>296.74</v>
       </c>
       <c r="AQ2" s="8" t="n">
-        <v>53.97</v>
+        <v>29.57</v>
       </c>
       <c r="AR2" s="8" t="n">
-        <v>0.05</v>
+        <v>1.07</v>
       </c>
       <c r="AS2" s="8" t="n">
-        <v>-33.63</v>
+        <v>-1.35</v>
       </c>
       <c r="AT2" s="8" t="n">
-        <v>45.66</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AU2" s="8" t="inlineStr"/>
       <c r="AV2" s="8" t="inlineStr"/>
@@ -5747,22 +6021,22 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>CLOSE_LIFECYCLE_PD</t>
+          <t>LOOSE_MATCH_SL_GUARD</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>533702297</t>
+          <t>534643103</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>46170.79517361111</v>
+        <v>46171.82914351852</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>46170.79518518518</v>
+        <v>46171.83998842593</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>4389.42</v>
+        <v>4530.5775</v>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
@@ -5770,31 +6044,31 @@
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>4389.2</v>
+        <v>4534.57</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>-0.88</v>
+        <v>15.97</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>-0.22</v>
+        <v>2.38</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>-0.22</v>
+        <v>3.62</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>-0.22</v>
+        <v>6.05</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>-0.22</v>
+        <v>3.92</v>
       </c>
       <c r="N3" s="8" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>[sl 4530.65]</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="P3" s="8" t="inlineStr"/>
@@ -5812,13 +6086,13 @@
       <c r="AB3" s="8" t="inlineStr"/>
       <c r="AC3" s="8" t="inlineStr"/>
       <c r="AD3" s="9" t="n">
-        <v>46170.75</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="AE3" s="9" t="n">
-        <v>46170.8125</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="AF3" s="8" t="n">
-        <v>4387.36</v>
+        <v>4564.21</v>
       </c>
       <c r="AG3" s="8" t="inlineStr">
         <is>
@@ -5826,10 +6100,10 @@
         </is>
       </c>
       <c r="AH3" s="8" t="n">
-        <v>4389.13</v>
+        <v>4534.52</v>
       </c>
       <c r="AI3" s="8" t="n">
-        <v>1.77</v>
+        <v>-29.69</v>
       </c>
       <c r="AJ3" s="8" t="inlineStr"/>
       <c r="AK3" s="8" t="inlineStr"/>
@@ -5837,7 +6111,7 @@
       <c r="AM3" s="8" t="inlineStr"/>
       <c r="AN3" s="8" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="AO3" s="8" t="inlineStr">
@@ -5846,37 +6120,25 @@
         </is>
       </c>
       <c r="AP3" s="8" t="n">
-        <v>650.5700000000001</v>
+        <v>539.72</v>
       </c>
       <c r="AQ3" s="8" t="n">
-        <v>65.05</v>
+        <v>53.97</v>
       </c>
       <c r="AR3" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AS3" s="8" t="n">
-        <v>2.06</v>
+        <v>-33.63</v>
       </c>
       <c r="AT3" s="8" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="AU3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" s="8" t="n"/>
-      <c r="AW3" s="8" t="n">
-        <v>4387.36</v>
-      </c>
-      <c r="AX3" s="8" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="AY3" s="8" t="inlineStr">
-        <is>
-          <t>M5 4387.36</t>
-        </is>
-      </c>
+        <v>45.66</v>
+      </c>
+      <c r="AU3" s="8" t="inlineStr"/>
+      <c r="AV3" s="8" t="inlineStr"/>
+      <c r="AW3" s="8" t="inlineStr"/>
+      <c r="AX3" s="8" t="inlineStr"/>
+      <c r="AY3" s="8" t="inlineStr"/>
       <c r="AZ3" s="8" t="inlineStr"/>
       <c r="BA3" s="8" t="inlineStr"/>
       <c r="BB3" s="8" t="inlineStr"/>
@@ -5890,8 +6152,159 @@
       <c r="BJ3" s="8" t="inlineStr"/>
       <c r="BK3" s="8" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>CLOSE_LIFECYCLE_PD</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>533702297</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>46170.79517361111</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>46170.79518518518</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>4389.42</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>4389.2</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>PD Zone fill che</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>[M5_M15]_S2</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="8" t="inlineStr"/>
+      <c r="V4" s="8" t="inlineStr"/>
+      <c r="W4" s="8" t="inlineStr"/>
+      <c r="X4" s="8" t="inlineStr"/>
+      <c r="Y4" s="8" t="inlineStr"/>
+      <c r="Z4" s="8" t="inlineStr"/>
+      <c r="AA4" s="8" t="inlineStr"/>
+      <c r="AB4" s="8" t="inlineStr"/>
+      <c r="AC4" s="8" t="inlineStr"/>
+      <c r="AD4" s="9" t="n">
+        <v>46170.75</v>
+      </c>
+      <c r="AE4" s="9" t="n">
+        <v>46170.8125</v>
+      </c>
+      <c r="AF4" s="8" t="n">
+        <v>4387.36</v>
+      </c>
+      <c r="AG4" s="8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="AH4" s="8" t="n">
+        <v>4389.13</v>
+      </c>
+      <c r="AI4" s="8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ4" s="8" t="inlineStr"/>
+      <c r="AK4" s="8" t="inlineStr"/>
+      <c r="AL4" s="8" t="inlineStr"/>
+      <c r="AM4" s="8" t="inlineStr"/>
+      <c r="AN4" s="8" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO4" s="8" t="inlineStr">
+        <is>
+          <t>LOOSE</t>
+        </is>
+      </c>
+      <c r="AP4" s="8" t="n">
+        <v>650.5700000000001</v>
+      </c>
+      <c r="AQ4" s="8" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="AR4" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AS4" s="8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT4" s="8" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="AU4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="8" t="n"/>
+      <c r="AW4" s="8" t="n">
+        <v>4387.36</v>
+      </c>
+      <c r="AX4" s="8" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="AY4" s="8" t="inlineStr">
+        <is>
+          <t>M5 4387.36</t>
+        </is>
+      </c>
+      <c r="AZ4" s="8" t="inlineStr"/>
+      <c r="BA4" s="8" t="inlineStr"/>
+      <c r="BB4" s="8" t="inlineStr"/>
+      <c r="BC4" s="8" t="inlineStr"/>
+      <c r="BD4" s="8" t="inlineStr"/>
+      <c r="BE4" s="8" t="inlineStr"/>
+      <c r="BF4" s="8" t="inlineStr"/>
+      <c r="BG4" s="8" t="inlineStr"/>
+      <c r="BH4" s="8" t="inlineStr"/>
+      <c r="BI4" s="8" t="inlineStr"/>
+      <c r="BJ4" s="8" t="inlineStr"/>
+      <c r="BK4" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BK3"/>
+  <autoFilter ref="A1:BK4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5902,7 +6315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK28"/>
+  <dimension ref="A1:BK30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5918,7 +6331,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
@@ -6295,54 +6708,54 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>533514424</t>
+          <t>532987481</t>
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>46170.8722337963</v>
+        <v>46170.39285879629</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>46170.91012731481</v>
+        <v>46170.40341435185</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>4425.155</v>
+        <v>4420.57</v>
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H2" s="10" t="n">
-        <v>4426.98</v>
+        <v>4426.11</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>7.300000000000002</v>
+        <v>-22.16</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>2.03</v>
+        <v>-5.54</v>
       </c>
       <c r="K2" s="10" t="n">
-        <v>3.78</v>
+        <v>-5.54</v>
       </c>
       <c r="L2" s="10" t="n">
-        <v>6.29</v>
+        <v>-5.54</v>
       </c>
       <c r="M2" s="10" t="n">
-        <v>-4.8</v>
+        <v>-5.54</v>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>[sl 4431.78]</t>
+          <t>[sl 4420.57]</t>
         </is>
       </c>
       <c r="O2" s="10" t="inlineStr">
         <is>
-          <t>[M30_H1_H4]_S2</t>
+          <t>[M15_H1]_S2</t>
         </is>
       </c>
       <c r="P2" s="10" t="inlineStr"/>
@@ -6384,10 +6797,10 @@
       <c r="AZ2" s="10" t="inlineStr"/>
       <c r="BA2" s="10" t="inlineStr"/>
       <c r="BB2" s="11" t="n">
-        <v>46170.75</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="BC2" s="10" t="n">
-        <v>4389.13</v>
+        <v>4386.33</v>
       </c>
       <c r="BD2" s="10" t="inlineStr">
         <is>
@@ -6395,10 +6808,10 @@
         </is>
       </c>
       <c r="BE2" s="10" t="n">
-        <v>176.02</v>
+        <v>304.28</v>
       </c>
       <c r="BF2" s="10" t="n">
-        <v>37.85</v>
+        <v>39.78</v>
       </c>
       <c r="BG2" s="10" t="inlineStr"/>
       <c r="BH2" s="10" t="inlineStr"/>
@@ -7485,54 +7898,54 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>534919533</t>
+          <t>534712433</t>
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>46171.98751157407</v>
+        <v>46171.87508101852</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>46171.9875462963</v>
+        <v>46171.88037037037</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>4565.07</v>
+        <v>4521.0625</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H12" s="10" t="n">
-        <v>4563.77</v>
+        <v>4524.14</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>5.2</v>
+        <v>12.31</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.3</v>
+        <v>3.25</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>1.3</v>
+        <v>3.18</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>1.3</v>
+        <v>6.06</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>1.3</v>
+        <v>-0.18</v>
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>[sl 4524.32]</t>
         </is>
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
-          <t>[M15_M30_H1]_S2</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr"/>
@@ -7574,21 +7987,21 @@
       <c r="AZ12" s="10" t="inlineStr"/>
       <c r="BA12" s="10" t="inlineStr"/>
       <c r="BB12" s="11" t="n">
-        <v>46170.60416666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="BC12" s="10" t="n">
-        <v>4386.33</v>
+        <v>4534.52</v>
       </c>
       <c r="BD12" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="BE12" s="10" t="n">
-        <v>1992.02</v>
+        <v>120.12</v>
       </c>
       <c r="BF12" s="10" t="n">
-        <v>177.44</v>
+        <v>10.38</v>
       </c>
       <c r="BG12" s="10" t="inlineStr"/>
       <c r="BH12" s="10" t="inlineStr"/>
@@ -7604,54 +8017,54 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>534962292</t>
+          <t>534919533</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>46172.00015046296</v>
+        <v>46171.98751157407</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>46172.01085648148</v>
+        <v>46171.9875462963</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>4566.98</v>
+        <v>4565.07</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H13" s="10" t="n">
-        <v>4571.73</v>
+        <v>4563.77</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>2.64</v>
+        <v>1.3</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>3.39</v>
+        <v>1.3</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>6.47</v>
+        <v>1.3</v>
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>[sl 4565.26]</t>
+          <t>PD Zone fill che</t>
         </is>
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>[M15_M30_H1]_S2</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr"/>
@@ -7693,21 +8106,21 @@
       <c r="AZ13" s="10" t="inlineStr"/>
       <c r="BA13" s="10" t="inlineStr"/>
       <c r="BB13" s="11" t="n">
-        <v>46171.79166666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="BC13" s="10" t="n">
-        <v>4534.52</v>
+        <v>4386.33</v>
       </c>
       <c r="BD13" s="10" t="inlineStr">
         <is>
-          <t>SL_GUARD_CLOSE</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="BE13" s="10" t="n">
-        <v>300.22</v>
+        <v>1992.02</v>
       </c>
       <c r="BF13" s="10" t="n">
-        <v>37.21</v>
+        <v>177.44</v>
       </c>
       <c r="BG13" s="10" t="inlineStr"/>
       <c r="BH13" s="10" t="inlineStr"/>
@@ -7728,49 +8141,49 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>535341125</t>
+          <t>534962292</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>46174.56412037037</v>
+        <v>46172.00015046296</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>46174.570625</v>
+        <v>46172.01085648148</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>4519.092500000001</v>
+        <v>4566.98</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H14" s="10" t="n">
-        <v>4515.68</v>
+        <v>4571.73</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>13.69</v>
+        <v>19</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>1.75</v>
+        <v>6.47</v>
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>[sl 4517.42]</t>
+          <t>[sl 4565.26]</t>
         </is>
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr"/>
@@ -7812,21 +8225,21 @@
       <c r="AZ14" s="10" t="inlineStr"/>
       <c r="BA14" s="10" t="inlineStr"/>
       <c r="BB14" s="11" t="n">
-        <v>46175.36458333334</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="BC14" s="10" t="n">
-        <v>4463.18</v>
+        <v>4534.52</v>
       </c>
       <c r="BD14" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="BE14" s="10" t="n">
-        <v>1152.67</v>
+        <v>300.22</v>
       </c>
       <c r="BF14" s="10" t="n">
-        <v>52.5</v>
+        <v>37.21</v>
       </c>
       <c r="BG14" s="10" t="inlineStr"/>
       <c r="BH14" s="10" t="inlineStr"/>
@@ -7847,17 +8260,17 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>534365910</t>
+          <t>535341125</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>46174.61928240741</v>
+        <v>46174.56412037037</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>46174.62296296296</v>
+        <v>46174.570625</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>4501.66</v>
+        <v>4519.092500000001</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
@@ -7865,26 +8278,26 @@
         </is>
       </c>
       <c r="H15" s="10" t="n">
-        <v>4501.15</v>
+        <v>4515.68</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>2.08</v>
+        <v>13.69</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.52</v>
+        <v>2.18</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>0.52</v>
+        <v>3.51</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>0.52</v>
+        <v>6.25</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>0.52</v>
+        <v>1.75</v>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>[sl 4501.66]</t>
+          <t>[sl 4517.42]</t>
         </is>
       </c>
       <c r="O15" s="10" t="inlineStr">
@@ -7942,10 +8355,10 @@
         </is>
       </c>
       <c r="BE15" s="10" t="n">
-        <v>1073.23</v>
+        <v>1152.67</v>
       </c>
       <c r="BF15" s="10" t="n">
-        <v>37.97</v>
+        <v>52.5</v>
       </c>
       <c r="BG15" s="10" t="inlineStr"/>
       <c r="BH15" s="10" t="inlineStr"/>
@@ -7961,49 +8374,49 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>535430453</t>
+          <t>534365910</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>46174.66325231481</v>
+        <v>46174.61928240741</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>46174.66327546296</v>
+        <v>46174.62296296296</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>4496.13</v>
+        <v>4501.66</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>4496.76</v>
+        <v>4501.15</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.75</v>
+        <v>0.52</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>0.75</v>
+        <v>0.52</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>0.75</v>
+        <v>0.52</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>0.75</v>
+        <v>0.52</v>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>[sl 4501.66]</t>
         </is>
       </c>
       <c r="O16" s="10" t="inlineStr">
@@ -8050,21 +8463,21 @@
       <c r="AZ16" s="10" t="inlineStr"/>
       <c r="BA16" s="10" t="inlineStr"/>
       <c r="BB16" s="11" t="n">
-        <v>46174.41666666666</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="BC16" s="10" t="n">
-        <v>4525.13</v>
+        <v>4463.18</v>
       </c>
       <c r="BD16" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="BE16" s="10" t="n">
-        <v>355.08</v>
+        <v>1073.23</v>
       </c>
       <c r="BF16" s="10" t="n">
-        <v>28.37</v>
+        <v>37.97</v>
       </c>
       <c r="BG16" s="10" t="inlineStr"/>
       <c r="BH16" s="10" t="inlineStr"/>
@@ -8080,54 +8493,54 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>534621735</t>
+          <t>535430453</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>46174.88290509259</v>
+        <v>46174.66325231481</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>46175.01981481481</v>
+        <v>46174.66327546296</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>4467.2</v>
+        <v>4496.13</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H17" s="10" t="n">
-        <v>4489.03</v>
+        <v>4496.76</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>-86.64</v>
+        <v>3</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>-21.66</v>
+        <v>0.75</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>-21.66</v>
+        <v>0.75</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>-21.66</v>
+        <v>0.75</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>-21.66</v>
+        <v>0.75</v>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>MT5_CLOSE</t>
+          <t>PD Zone fill che</t>
         </is>
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
-          <t>[H1_H4_H12]_S2</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr"/>
@@ -8169,21 +8582,21 @@
       <c r="AZ17" s="10" t="inlineStr"/>
       <c r="BA17" s="10" t="inlineStr"/>
       <c r="BB17" s="11" t="n">
-        <v>46175.36458333334</v>
+        <v>46174.41666666666</v>
       </c>
       <c r="BC17" s="10" t="n">
-        <v>4463.18</v>
+        <v>4525.13</v>
       </c>
       <c r="BD17" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="BE17" s="10" t="n">
-        <v>693.62</v>
+        <v>355.08</v>
       </c>
       <c r="BF17" s="10" t="n">
-        <v>25.85</v>
+        <v>28.37</v>
       </c>
       <c r="BG17" s="10" t="inlineStr"/>
       <c r="BH17" s="10" t="inlineStr"/>
@@ -8199,22 +8612,22 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>536092728</t>
+          <t>535530550</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>46175.52091435185</v>
+        <v>46174.79511574074</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>46175.5209837963</v>
+        <v>46174.8089699074</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>4504.18</v>
+        <v>4505.55</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -8222,31 +8635,31 @@
         </is>
       </c>
       <c r="H18" s="10" t="n">
-        <v>4504.06</v>
+        <v>4500.6</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>1.52</v>
+        <v>20</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.38</v>
+        <v>2.25</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0.38</v>
+        <v>3.08</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>0.38</v>
+        <v>6.14</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>0.38</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>[sl 4509.08]</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
-          <t>[M1_M5_M15]_S2</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr"/>
@@ -8299,10 +8712,10 @@
         </is>
       </c>
       <c r="BE18" s="10" t="n">
-        <v>225.12</v>
+        <v>820.03</v>
       </c>
       <c r="BF18" s="10" t="n">
-        <v>40.88</v>
+        <v>37.42</v>
       </c>
       <c r="BG18" s="10" t="inlineStr"/>
       <c r="BH18" s="10" t="inlineStr"/>
@@ -8323,7 +8736,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>536096897</t>
+          <t>536092728</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
@@ -8341,7 +8754,7 @@
         </is>
       </c>
       <c r="H19" s="10" t="n">
-        <v>4503.99</v>
+        <v>4504.06</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>1.52</v>
@@ -8365,7 +8778,7 @@
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>[M1_M5_M15]_S2</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr"/>
@@ -8421,7 +8834,7 @@
         <v>225.12</v>
       </c>
       <c r="BF19" s="10" t="n">
-        <v>40.81</v>
+        <v>40.88</v>
       </c>
       <c r="BG19" s="10" t="inlineStr"/>
       <c r="BH19" s="10" t="inlineStr"/>
@@ -8442,17 +8855,17 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>536118248</t>
+          <t>536096897</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>46175.54528935185</v>
+        <v>46175.52091435185</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>46175.54528935185</v>
+        <v>46175.5209837963</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>4515.65</v>
+        <v>4504.18</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -8460,22 +8873,22 @@
         </is>
       </c>
       <c r="H20" s="10" t="n">
-        <v>4515.81</v>
+        <v>4503.99</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>-0.64</v>
+        <v>1.52</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.38</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.38</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.38</v>
       </c>
       <c r="M20" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.38</v>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
@@ -8484,7 +8897,7 @@
       </c>
       <c r="O20" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="P20" s="10" t="inlineStr"/>
@@ -8537,10 +8950,10 @@
         </is>
       </c>
       <c r="BE20" s="10" t="n">
-        <v>260.22</v>
+        <v>225.12</v>
       </c>
       <c r="BF20" s="10" t="n">
-        <v>52.63</v>
+        <v>40.81</v>
       </c>
       <c r="BG20" s="10" t="inlineStr"/>
       <c r="BH20" s="10" t="inlineStr"/>
@@ -8561,17 +8974,17 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>536140461</t>
+          <t>536118248</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>46175.5775</v>
+        <v>46175.54528935185</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>46175.57751157408</v>
+        <v>46175.54528935185</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>4519.67</v>
+        <v>4515.65</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
@@ -8579,22 +8992,22 @@
         </is>
       </c>
       <c r="H21" s="10" t="n">
-        <v>4519.72</v>
+        <v>4515.81</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>0.16</v>
+        <v>-0.64</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
@@ -8603,7 +9016,7 @@
       </c>
       <c r="O21" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr"/>
@@ -8656,10 +9069,10 @@
         </is>
       </c>
       <c r="BE21" s="10" t="n">
-        <v>306.6</v>
+        <v>260.22</v>
       </c>
       <c r="BF21" s="10" t="n">
-        <v>56.54</v>
+        <v>52.63</v>
       </c>
       <c r="BG21" s="10" t="inlineStr"/>
       <c r="BH21" s="10" t="inlineStr"/>
@@ -8680,17 +9093,17 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>536180512</t>
+          <t>536140461</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>46175.65538194445</v>
+        <v>46175.5775</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>46175.65540509259</v>
+        <v>46175.57751157408</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>4531.6</v>
+        <v>4519.67</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -8698,7 +9111,7 @@
         </is>
       </c>
       <c r="H22" s="10" t="n">
-        <v>4531.65</v>
+        <v>4519.72</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>0.16</v>
@@ -8722,7 +9135,7 @@
       </c>
       <c r="O22" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr"/>
@@ -8775,10 +9188,10 @@
         </is>
       </c>
       <c r="BE22" s="10" t="n">
-        <v>418.75</v>
+        <v>306.6</v>
       </c>
       <c r="BF22" s="10" t="n">
-        <v>68.47</v>
+        <v>56.54</v>
       </c>
       <c r="BG22" s="10" t="inlineStr"/>
       <c r="BH22" s="10" t="inlineStr"/>
@@ -8794,22 +9207,22 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>536129864</t>
+          <t>536180512</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>46175.87108796297</v>
+        <v>46175.65538194445</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>46175.875</v>
+        <v>46175.65540509259</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>4513.52</v>
+        <v>4531.6</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
@@ -8817,31 +9230,31 @@
         </is>
       </c>
       <c r="H23" s="10" t="n">
-        <v>4515.12</v>
+        <v>4531.65</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>-6.2</v>
+        <v>0.16</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>-1.55</v>
+        <v>0.04</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>-1.55</v>
+        <v>0.04</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>-1.55</v>
+        <v>0.04</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>-1.55</v>
+        <v>0.04</v>
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>#536129864 by #536052988</t>
+          <t>PD Zone fill che</t>
         </is>
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
-          <t>[M5_M30_H1]_S2</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="P23" s="10" t="inlineStr"/>
@@ -8894,10 +9307,10 @@
         </is>
       </c>
       <c r="BE23" s="10" t="n">
-        <v>729.37</v>
+        <v>418.75</v>
       </c>
       <c r="BF23" s="10" t="n">
-        <v>51.94</v>
+        <v>68.47</v>
       </c>
       <c r="BG23" s="10" t="inlineStr"/>
       <c r="BH23" s="10" t="inlineStr"/>
@@ -8918,49 +9331,49 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>536634210</t>
+          <t>536611496</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>46176.42392361111</v>
+        <v>46176.37560185185</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>46176.42395833333</v>
+        <v>46176.37864583333</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>4479.58</v>
+        <v>4472.38</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H24" s="10" t="n">
-        <v>4479.44</v>
+        <v>4481.32</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>-0.16</v>
+        <v>-34.68</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>-0.04</v>
+        <v>-8.67</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>-0.04</v>
+        <v>-8.67</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>-0.04</v>
+        <v>-8.67</v>
       </c>
       <c r="M24" s="10" t="n">
-        <v>-0.04</v>
+        <v>-8.67</v>
       </c>
       <c r="N24" s="10" t="inlineStr">
         <is>
-          <t>Fill Trend Reche</t>
+          <t>SL Guard Group a</t>
         </is>
       </c>
       <c r="O24" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr"/>
@@ -9002,21 +9415,21 @@
       <c r="AZ24" s="10" t="inlineStr"/>
       <c r="BA24" s="10" t="inlineStr"/>
       <c r="BB24" s="11" t="n">
-        <v>46177.23958333334</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="BC24" s="10" t="n">
-        <v>4445.39</v>
+        <v>4463.18</v>
       </c>
       <c r="BD24" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="BE24" s="10" t="n">
-        <v>1174.55</v>
+        <v>1455.87</v>
       </c>
       <c r="BF24" s="10" t="n">
-        <v>34.05</v>
+        <v>18.14</v>
       </c>
       <c r="BG24" s="10" t="inlineStr"/>
       <c r="BH24" s="10" t="inlineStr"/>
@@ -9032,54 +9445,54 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>537233013</t>
+          <t>536634210</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>46177.17019675926</v>
+        <v>46176.42392361111</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>46177.18942129629</v>
+        <v>46176.42395833333</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>4436.19</v>
+        <v>4479.58</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H25" s="10" t="n">
-        <v>4441.21</v>
+        <v>4479.44</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>-18.32</v>
+        <v>-0.16</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>-4.58</v>
+        <v>-0.04</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>-4.58</v>
+        <v>-0.04</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>-4.58</v>
+        <v>-0.04</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>-4.58</v>
+        <v>-0.04</v>
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>SL Guard Group a</t>
+          <t>Fill Trend Reche</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15_M30]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr"/>
@@ -9121,10 +9534,10 @@
       <c r="AZ25" s="10" t="inlineStr"/>
       <c r="BA25" s="10" t="inlineStr"/>
       <c r="BB25" s="11" t="n">
-        <v>46178.42708333334</v>
+        <v>46177.23958333334</v>
       </c>
       <c r="BC25" s="10" t="n">
-        <v>4436.72</v>
+        <v>4445.39</v>
       </c>
       <c r="BD25" s="10" t="inlineStr">
         <is>
@@ -9132,10 +9545,10 @@
         </is>
       </c>
       <c r="BE25" s="10" t="n">
-        <v>1809.92</v>
+        <v>1174.55</v>
       </c>
       <c r="BF25" s="10" t="n">
-        <v>4.49</v>
+        <v>34.05</v>
       </c>
       <c r="BG25" s="10" t="inlineStr"/>
       <c r="BH25" s="10" t="inlineStr"/>
@@ -9151,22 +9564,22 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>537277914</t>
+          <t>537233013</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>46177.34267361111</v>
+        <v>46177.17019675926</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>46177.34271990741</v>
+        <v>46177.18942129629</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>4454.16</v>
+        <v>4436.19</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
@@ -9174,31 +9587,31 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>4453.59</v>
+        <v>4441.21</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>2.56</v>
+        <v>-18.32</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.64</v>
+        <v>-4.58</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0.64</v>
+        <v>-4.58</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>0.64</v>
+        <v>-4.58</v>
       </c>
       <c r="M26" s="10" t="n">
-        <v>0.64</v>
+        <v>-4.58</v>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>SL Guard Group a</t>
         </is>
       </c>
       <c r="O26" s="10" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>[M5_M15_M30]_S2</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr"/>
@@ -9251,10 +9664,10 @@
         </is>
       </c>
       <c r="BE26" s="10" t="n">
-        <v>1561.55</v>
+        <v>1809.92</v>
       </c>
       <c r="BF26" s="10" t="n">
-        <v>16.87</v>
+        <v>4.49</v>
       </c>
       <c r="BG26" s="10" t="inlineStr"/>
       <c r="BH26" s="10" t="inlineStr"/>
@@ -9275,40 +9688,40 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>537984794</t>
+          <t>537277914</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>46178.35443287037</v>
+        <v>46177.34267361111</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>46178.35444444444</v>
+        <v>46177.34271990741</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>4457.81</v>
+        <v>4454.16</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H27" s="10" t="n">
-        <v>4457.7</v>
+        <v>4453.59</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>0.72</v>
+        <v>2.56</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.18</v>
+        <v>0.64</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>0.18</v>
+        <v>0.64</v>
       </c>
       <c r="L27" s="10" t="n">
-        <v>0.18</v>
+        <v>0.64</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>0.18</v>
+        <v>0.64</v>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
@@ -9317,7 +9730,7 @@
       </c>
       <c r="O27" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr"/>
@@ -9359,10 +9772,10 @@
       <c r="AZ27" s="10" t="inlineStr"/>
       <c r="BA27" s="10" t="inlineStr"/>
       <c r="BB27" s="11" t="n">
-        <v>46177.23958333334</v>
+        <v>46178.42708333334</v>
       </c>
       <c r="BC27" s="10" t="n">
-        <v>4445.39</v>
+        <v>4436.72</v>
       </c>
       <c r="BD27" s="10" t="inlineStr">
         <is>
@@ -9370,10 +9783,10 @@
         </is>
       </c>
       <c r="BE27" s="10" t="n">
-        <v>1605.38</v>
+        <v>1561.55</v>
       </c>
       <c r="BF27" s="10" t="n">
-        <v>12.31</v>
+        <v>16.87</v>
       </c>
       <c r="BG27" s="10" t="inlineStr"/>
       <c r="BH27" s="10" t="inlineStr"/>
@@ -9394,40 +9807,40 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>537975016</t>
+          <t>537416021</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>46178.35872685185</v>
+        <v>46177.5493287037</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>46178.35872685185</v>
+        <v>46177.54938657407</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>4466.56</v>
+        <v>4472.07</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>4466.12</v>
+        <v>4472.82</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>-0.64</v>
+        <v>0.32</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.08</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.08</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.08</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.08</v>
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
@@ -9436,7 +9849,7 @@
       </c>
       <c r="O28" s="10" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr"/>
@@ -9478,10 +9891,10 @@
       <c r="AZ28" s="10" t="inlineStr"/>
       <c r="BA28" s="10" t="inlineStr"/>
       <c r="BB28" s="11" t="n">
-        <v>46177.23958333334</v>
+        <v>46178.42708333334</v>
       </c>
       <c r="BC28" s="10" t="n">
-        <v>4445.39</v>
+        <v>4436.72</v>
       </c>
       <c r="BD28" s="10" t="inlineStr">
         <is>
@@ -9489,10 +9902,10 @@
         </is>
       </c>
       <c r="BE28" s="10" t="n">
-        <v>1611.57</v>
+        <v>1263.97</v>
       </c>
       <c r="BF28" s="10" t="n">
-        <v>20.73</v>
+        <v>36.1</v>
       </c>
       <c r="BG28" s="10" t="inlineStr"/>
       <c r="BH28" s="10" t="inlineStr"/>
@@ -9500,8 +9913,246 @@
       <c r="BJ28" s="10" t="inlineStr"/>
       <c r="BK28" s="10" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>LIVE_ONLY</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>537984794</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>46178.35443287037</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>46178.35444444444</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>4457.81</v>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>4457.7</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>PD Zone fill che</t>
+        </is>
+      </c>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>M15_S2_P2</t>
+        </is>
+      </c>
+      <c r="P29" s="10" t="inlineStr"/>
+      <c r="Q29" s="10" t="inlineStr"/>
+      <c r="R29" s="10" t="inlineStr"/>
+      <c r="S29" s="10" t="inlineStr"/>
+      <c r="T29" s="10" t="inlineStr"/>
+      <c r="U29" s="10" t="inlineStr"/>
+      <c r="V29" s="10" t="inlineStr"/>
+      <c r="W29" s="10" t="inlineStr"/>
+      <c r="X29" s="10" t="inlineStr"/>
+      <c r="Y29" s="10" t="inlineStr"/>
+      <c r="Z29" s="10" t="inlineStr"/>
+      <c r="AA29" s="10" t="inlineStr"/>
+      <c r="AB29" s="10" t="inlineStr"/>
+      <c r="AC29" s="10" t="inlineStr"/>
+      <c r="AD29" s="10" t="inlineStr"/>
+      <c r="AE29" s="10" t="inlineStr"/>
+      <c r="AF29" s="10" t="inlineStr"/>
+      <c r="AG29" s="10" t="inlineStr"/>
+      <c r="AH29" s="10" t="inlineStr"/>
+      <c r="AI29" s="10" t="inlineStr"/>
+      <c r="AJ29" s="10" t="inlineStr"/>
+      <c r="AK29" s="10" t="inlineStr"/>
+      <c r="AL29" s="10" t="inlineStr"/>
+      <c r="AM29" s="10" t="inlineStr"/>
+      <c r="AN29" s="10" t="inlineStr"/>
+      <c r="AO29" s="10" t="inlineStr"/>
+      <c r="AP29" s="10" t="inlineStr"/>
+      <c r="AQ29" s="10" t="inlineStr"/>
+      <c r="AR29" s="10" t="inlineStr"/>
+      <c r="AS29" s="10" t="inlineStr"/>
+      <c r="AT29" s="10" t="inlineStr"/>
+      <c r="AU29" s="10" t="inlineStr"/>
+      <c r="AV29" s="10" t="inlineStr"/>
+      <c r="AW29" s="10" t="inlineStr"/>
+      <c r="AX29" s="10" t="inlineStr"/>
+      <c r="AY29" s="10" t="inlineStr"/>
+      <c r="AZ29" s="10" t="inlineStr"/>
+      <c r="BA29" s="10" t="inlineStr"/>
+      <c r="BB29" s="11" t="n">
+        <v>46177.23958333334</v>
+      </c>
+      <c r="BC29" s="10" t="n">
+        <v>4445.39</v>
+      </c>
+      <c r="BD29" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="BE29" s="10" t="n">
+        <v>1605.38</v>
+      </c>
+      <c r="BF29" s="10" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="BG29" s="10" t="inlineStr"/>
+      <c r="BH29" s="10" t="inlineStr"/>
+      <c r="BI29" s="10" t="inlineStr"/>
+      <c r="BJ29" s="10" t="inlineStr"/>
+      <c r="BK29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>LIVE_ONLY</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>537975016</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>46178.35872685185</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>46178.35872685185</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>4466.56</v>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>4466.12</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L30" s="10" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M30" s="10" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>PD Zone fill che</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>M15_S2_P1</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="inlineStr"/>
+      <c r="Q30" s="10" t="inlineStr"/>
+      <c r="R30" s="10" t="inlineStr"/>
+      <c r="S30" s="10" t="inlineStr"/>
+      <c r="T30" s="10" t="inlineStr"/>
+      <c r="U30" s="10" t="inlineStr"/>
+      <c r="V30" s="10" t="inlineStr"/>
+      <c r="W30" s="10" t="inlineStr"/>
+      <c r="X30" s="10" t="inlineStr"/>
+      <c r="Y30" s="10" t="inlineStr"/>
+      <c r="Z30" s="10" t="inlineStr"/>
+      <c r="AA30" s="10" t="inlineStr"/>
+      <c r="AB30" s="10" t="inlineStr"/>
+      <c r="AC30" s="10" t="inlineStr"/>
+      <c r="AD30" s="10" t="inlineStr"/>
+      <c r="AE30" s="10" t="inlineStr"/>
+      <c r="AF30" s="10" t="inlineStr"/>
+      <c r="AG30" s="10" t="inlineStr"/>
+      <c r="AH30" s="10" t="inlineStr"/>
+      <c r="AI30" s="10" t="inlineStr"/>
+      <c r="AJ30" s="10" t="inlineStr"/>
+      <c r="AK30" s="10" t="inlineStr"/>
+      <c r="AL30" s="10" t="inlineStr"/>
+      <c r="AM30" s="10" t="inlineStr"/>
+      <c r="AN30" s="10" t="inlineStr"/>
+      <c r="AO30" s="10" t="inlineStr"/>
+      <c r="AP30" s="10" t="inlineStr"/>
+      <c r="AQ30" s="10" t="inlineStr"/>
+      <c r="AR30" s="10" t="inlineStr"/>
+      <c r="AS30" s="10" t="inlineStr"/>
+      <c r="AT30" s="10" t="inlineStr"/>
+      <c r="AU30" s="10" t="inlineStr"/>
+      <c r="AV30" s="10" t="inlineStr"/>
+      <c r="AW30" s="10" t="inlineStr"/>
+      <c r="AX30" s="10" t="inlineStr"/>
+      <c r="AY30" s="10" t="inlineStr"/>
+      <c r="AZ30" s="10" t="inlineStr"/>
+      <c r="BA30" s="10" t="inlineStr"/>
+      <c r="BB30" s="11" t="n">
+        <v>46177.23958333334</v>
+      </c>
+      <c r="BC30" s="10" t="n">
+        <v>4445.39</v>
+      </c>
+      <c r="BD30" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="BE30" s="10" t="n">
+        <v>1611.57</v>
+      </c>
+      <c r="BF30" s="10" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="BG30" s="10" t="inlineStr"/>
+      <c r="BH30" s="10" t="inlineStr"/>
+      <c r="BI30" s="10" t="inlineStr"/>
+      <c r="BJ30" s="10" t="inlineStr"/>
+      <c r="BK30" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BK28"/>
+  <autoFilter ref="A1:BK30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9512,7 +10163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK6"/>
+  <dimension ref="A1:BK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9936,24 +10587,24 @@
       <c r="AB2" s="10" t="inlineStr"/>
       <c r="AC2" s="10" t="inlineStr"/>
       <c r="AD2" s="11" t="n">
-        <v>46170.60416666666</v>
+        <v>46174.41666666666</v>
       </c>
       <c r="AE2" s="11" t="n">
-        <v>46170.75</v>
+        <v>46174.5</v>
       </c>
       <c r="AF2" s="10" t="n">
-        <v>4386.47</v>
+        <v>4515.69</v>
       </c>
       <c r="AG2" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH2" s="10" t="n">
-        <v>4386.33</v>
+        <v>4525.13</v>
       </c>
       <c r="AI2" s="10" t="n">
-        <v>0.14</v>
+        <v>9.44</v>
       </c>
       <c r="AJ2" s="10" t="inlineStr"/>
       <c r="AK2" s="10" t="inlineStr"/>
@@ -9970,11 +10621,23 @@
       <c r="AR2" s="10" t="inlineStr"/>
       <c r="AS2" s="10" t="inlineStr"/>
       <c r="AT2" s="10" t="inlineStr"/>
-      <c r="AU2" s="10" t="inlineStr"/>
-      <c r="AV2" s="10" t="inlineStr"/>
-      <c r="AW2" s="10" t="inlineStr"/>
-      <c r="AX2" s="10" t="inlineStr"/>
-      <c r="AY2" s="10" t="inlineStr"/>
+      <c r="AU2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" s="10" t="n"/>
+      <c r="AW2" s="10" t="n">
+        <v>4515.69</v>
+      </c>
+      <c r="AX2" s="10" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="AY2" s="10" t="inlineStr">
+        <is>
+          <t>M5 4515.69</t>
+        </is>
+      </c>
       <c r="AZ2" s="10" t="inlineStr"/>
       <c r="BA2" s="10" t="inlineStr"/>
       <c r="BB2" s="10" t="inlineStr"/>
@@ -9983,21 +10646,21 @@
       <c r="BE2" s="10" t="inlineStr"/>
       <c r="BF2" s="10" t="inlineStr"/>
       <c r="BG2" s="11" t="n">
-        <v>46171.40813657407</v>
+        <v>46174.66325231481</v>
       </c>
       <c r="BH2" s="10" t="n">
-        <v>4502.76</v>
+        <v>4496.76</v>
       </c>
       <c r="BI2" s="10" t="inlineStr">
         <is>
-          <t>[sl 4502.92]</t>
+          <t>PD Zone fill che</t>
         </is>
       </c>
       <c r="BJ2" s="10" t="n">
-        <v>1157.72</v>
+        <v>355.08</v>
       </c>
       <c r="BK2" s="10" t="n">
-        <v>116.43</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="3">
@@ -10039,24 +10702,24 @@
       <c r="AB3" s="10" t="inlineStr"/>
       <c r="AC3" s="10" t="inlineStr"/>
       <c r="AD3" s="11" t="n">
-        <v>46174.41666666666</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="AE3" s="11" t="n">
-        <v>46174.5</v>
+        <v>46175.45833333334</v>
       </c>
       <c r="AF3" s="10" t="n">
-        <v>4515.69</v>
+        <v>4502.48</v>
       </c>
       <c r="AG3" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH3" s="10" t="n">
-        <v>4525.13</v>
+        <v>4463.18</v>
       </c>
       <c r="AI3" s="10" t="n">
-        <v>9.44</v>
+        <v>39.3</v>
       </c>
       <c r="AJ3" s="10" t="inlineStr"/>
       <c r="AK3" s="10" t="inlineStr"/>
@@ -10064,7 +10727,7 @@
       <c r="AM3" s="10" t="inlineStr"/>
       <c r="AN3" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO3" s="10" t="inlineStr"/>
@@ -10073,23 +10736,11 @@
       <c r="AR3" s="10" t="inlineStr"/>
       <c r="AS3" s="10" t="inlineStr"/>
       <c r="AT3" s="10" t="inlineStr"/>
-      <c r="AU3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" s="10" t="n"/>
-      <c r="AW3" s="10" t="n">
-        <v>4515.69</v>
-      </c>
-      <c r="AX3" s="10" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="AY3" s="10" t="inlineStr">
-        <is>
-          <t>M5 4515.69</t>
-        </is>
-      </c>
+      <c r="AU3" s="10" t="inlineStr"/>
+      <c r="AV3" s="10" t="inlineStr"/>
+      <c r="AW3" s="10" t="inlineStr"/>
+      <c r="AX3" s="10" t="inlineStr"/>
+      <c r="AY3" s="10" t="inlineStr"/>
       <c r="AZ3" s="10" t="inlineStr"/>
       <c r="BA3" s="10" t="inlineStr"/>
       <c r="BB3" s="10" t="inlineStr"/>
@@ -10098,10 +10749,10 @@
       <c r="BE3" s="10" t="inlineStr"/>
       <c r="BF3" s="10" t="inlineStr"/>
       <c r="BG3" s="11" t="n">
-        <v>46174.66325231481</v>
+        <v>46175.52091435185</v>
       </c>
       <c r="BH3" s="10" t="n">
-        <v>4496.76</v>
+        <v>4503.99</v>
       </c>
       <c r="BI3" s="10" t="inlineStr">
         <is>
@@ -10109,10 +10760,10 @@
         </is>
       </c>
       <c r="BJ3" s="10" t="n">
-        <v>355.08</v>
+        <v>225.12</v>
       </c>
       <c r="BK3" s="10" t="n">
-        <v>28.37</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="4">
@@ -10154,24 +10805,24 @@
       <c r="AB4" s="10" t="inlineStr"/>
       <c r="AC4" s="10" t="inlineStr"/>
       <c r="AD4" s="11" t="n">
-        <v>46175.36458333334</v>
+        <v>46177.23958333334</v>
       </c>
       <c r="AE4" s="11" t="n">
-        <v>46175.45833333334</v>
+        <v>46177.28125</v>
       </c>
       <c r="AF4" s="10" t="n">
-        <v>4502.48</v>
+        <v>4461.57</v>
       </c>
       <c r="AG4" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH4" s="10" t="n">
-        <v>4463.18</v>
+        <v>4445.39</v>
       </c>
       <c r="AI4" s="10" t="n">
-        <v>39.3</v>
+        <v>-16.18</v>
       </c>
       <c r="AJ4" s="10" t="inlineStr"/>
       <c r="AK4" s="10" t="inlineStr"/>
@@ -10179,7 +10830,7 @@
       <c r="AM4" s="10" t="inlineStr"/>
       <c r="AN4" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO4" s="10" t="inlineStr"/>
@@ -10201,21 +10852,21 @@
       <c r="BE4" s="10" t="inlineStr"/>
       <c r="BF4" s="10" t="inlineStr"/>
       <c r="BG4" s="11" t="n">
-        <v>46175.52091435185</v>
+        <v>46176.42392361111</v>
       </c>
       <c r="BH4" s="10" t="n">
-        <v>4503.99</v>
+        <v>4479.44</v>
       </c>
       <c r="BI4" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill che</t>
+          <t>Fill Trend Reche</t>
         </is>
       </c>
       <c r="BJ4" s="10" t="n">
-        <v>225.12</v>
+        <v>1174.55</v>
       </c>
       <c r="BK4" s="10" t="n">
-        <v>40.81</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="5">
@@ -10257,24 +10908,24 @@
       <c r="AB5" s="10" t="inlineStr"/>
       <c r="AC5" s="10" t="inlineStr"/>
       <c r="AD5" s="11" t="n">
-        <v>46177.23958333334</v>
+        <v>46178.42708333334</v>
       </c>
       <c r="AE5" s="11" t="n">
-        <v>46177.28125</v>
+        <v>46178.52083333334</v>
       </c>
       <c r="AF5" s="10" t="n">
-        <v>4461.57</v>
+        <v>4439.68</v>
       </c>
       <c r="AG5" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH5" s="10" t="n">
-        <v>4445.39</v>
+        <v>4436.72</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>-16.18</v>
+        <v>2.96</v>
       </c>
       <c r="AJ5" s="10" t="inlineStr"/>
       <c r="AK5" s="10" t="inlineStr"/>
@@ -10291,11 +10942,23 @@
       <c r="AR5" s="10" t="inlineStr"/>
       <c r="AS5" s="10" t="inlineStr"/>
       <c r="AT5" s="10" t="inlineStr"/>
-      <c r="AU5" s="10" t="inlineStr"/>
-      <c r="AV5" s="10" t="inlineStr"/>
-      <c r="AW5" s="10" t="inlineStr"/>
-      <c r="AX5" s="10" t="inlineStr"/>
-      <c r="AY5" s="10" t="inlineStr"/>
+      <c r="AU5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="10" t="n"/>
+      <c r="AW5" s="10" t="n">
+        <v>4439.68</v>
+      </c>
+      <c r="AX5" s="10" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="AY5" s="10" t="inlineStr">
+        <is>
+          <t>M5 4439.68</t>
+        </is>
+      </c>
       <c r="AZ5" s="10" t="inlineStr"/>
       <c r="BA5" s="10" t="inlineStr"/>
       <c r="BB5" s="10" t="inlineStr"/>
@@ -10304,140 +10967,25 @@
       <c r="BE5" s="10" t="inlineStr"/>
       <c r="BF5" s="10" t="inlineStr"/>
       <c r="BG5" s="11" t="n">
-        <v>46176.42392361111</v>
+        <v>46177.5493287037</v>
       </c>
       <c r="BH5" s="10" t="n">
-        <v>4479.44</v>
+        <v>4472.82</v>
       </c>
       <c r="BI5" s="10" t="inlineStr">
         <is>
-          <t>Fill Trend Reche</t>
+          <t>PD Zone fill che</t>
         </is>
       </c>
       <c r="BJ5" s="10" t="n">
-        <v>1174.55</v>
+        <v>1263.97</v>
       </c>
       <c r="BK5" s="10" t="n">
-        <v>34.05</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
-      <c r="O6" s="10" t="inlineStr"/>
-      <c r="P6" s="10" t="inlineStr"/>
-      <c r="Q6" s="10" t="inlineStr"/>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
-      <c r="T6" s="10" t="inlineStr"/>
-      <c r="U6" s="10" t="inlineStr"/>
-      <c r="V6" s="10" t="inlineStr"/>
-      <c r="W6" s="10" t="inlineStr"/>
-      <c r="X6" s="10" t="inlineStr"/>
-      <c r="Y6" s="10" t="inlineStr"/>
-      <c r="Z6" s="10" t="inlineStr"/>
-      <c r="AA6" s="10" t="inlineStr"/>
-      <c r="AB6" s="10" t="inlineStr"/>
-      <c r="AC6" s="10" t="inlineStr"/>
-      <c r="AD6" s="11" t="n">
-        <v>46178.42708333334</v>
-      </c>
-      <c r="AE6" s="11" t="n">
-        <v>46178.52083333334</v>
-      </c>
-      <c r="AF6" s="10" t="n">
-        <v>4439.68</v>
-      </c>
-      <c r="AG6" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH6" s="10" t="n">
-        <v>4436.72</v>
-      </c>
-      <c r="AI6" s="10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AJ6" s="10" t="inlineStr"/>
-      <c r="AK6" s="10" t="inlineStr"/>
-      <c r="AL6" s="10" t="inlineStr"/>
-      <c r="AM6" s="10" t="inlineStr"/>
-      <c r="AN6" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO6" s="10" t="inlineStr"/>
-      <c r="AP6" s="10" t="inlineStr"/>
-      <c r="AQ6" s="10" t="inlineStr"/>
-      <c r="AR6" s="10" t="inlineStr"/>
-      <c r="AS6" s="10" t="inlineStr"/>
-      <c r="AT6" s="10" t="inlineStr"/>
-      <c r="AU6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" s="10" t="n"/>
-      <c r="AW6" s="10" t="n">
-        <v>4439.68</v>
-      </c>
-      <c r="AX6" s="10" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="AY6" s="10" t="inlineStr">
-        <is>
-          <t>M5 4439.68</t>
-        </is>
-      </c>
-      <c r="AZ6" s="10" t="inlineStr"/>
-      <c r="BA6" s="10" t="inlineStr"/>
-      <c r="BB6" s="10" t="inlineStr"/>
-      <c r="BC6" s="10" t="inlineStr"/>
-      <c r="BD6" s="10" t="inlineStr"/>
-      <c r="BE6" s="10" t="inlineStr"/>
-      <c r="BF6" s="10" t="inlineStr"/>
-      <c r="BG6" s="11" t="n">
-        <v>46177.34267361111</v>
-      </c>
-      <c r="BH6" s="10" t="n">
-        <v>4453.59</v>
-      </c>
-      <c r="BI6" s="10" t="inlineStr">
-        <is>
-          <t>PD Zone fill che</t>
-        </is>
-      </c>
-      <c r="BJ6" s="10" t="n">
-        <v>1561.55</v>
-      </c>
-      <c r="BK6" s="10" t="n">
-        <v>16.87</v>
+        <v>36.1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BK6"/>
+  <autoFilter ref="A1:BK5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10910,7 +11458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10976,16 +11524,16 @@
         </is>
       </c>
       <c r="D2" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="12" t="n">
-        <v>10.48</v>
+        <v>10.8</v>
       </c>
       <c r="F2" s="13" t="n">
         <v>46171.98751157407</v>
       </c>
       <c r="G2" s="13" t="n">
-        <v>46177.34267361111</v>
+        <v>46177.5493287037</v>
       </c>
     </row>
     <row r="3">
@@ -11025,7 +11573,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>#536129864 by #536052988</t>
+          <t>SL Guard Group a</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -11034,16 +11582,16 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>-6.2</v>
+        <v>-53</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>46175.87108796297</v>
+        <v>46176.37560185185</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>46175.87108796297</v>
+        <v>46177.17019675926</v>
       </c>
     </row>
     <row r="5">
@@ -11083,25 +11631,25 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>MT5_CLOSE</t>
+          <t>PD Zone fill rou</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-86.64</v>
+        <v>-5.57</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>46174.88290509259</v>
+        <v>46170.92326388889</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>46174.88290509259</v>
+        <v>46170.92326388889</v>
       </c>
     </row>
     <row r="7">
@@ -11112,25 +11660,25 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>PD Zone fill rou</t>
+          <t>[sl 4420.57]</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-5.57</v>
+        <v>-22.16</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>46170.92326388889</v>
+        <v>46170.39285879629</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>46170.92326388889</v>
+        <v>46170.39285879629</v>
       </c>
     </row>
     <row r="8">
@@ -11141,25 +11689,25 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>SL Guard Group a</t>
+          <t>[sl 4474.39]</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-18.32</v>
+        <v>-20.62</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>46177.17019675926</v>
+        <v>46170.92326388889</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>46177.17019675926</v>
+        <v>46170.92326388889</v>
       </c>
     </row>
     <row r="9">
@@ -11170,7 +11718,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>[sl 4431.78]</t>
+          <t>[sl 4498.95]</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -11182,13 +11730,13 @@
         <v>1</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>7.3</v>
+        <v>2.48</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>46170.8722337963</v>
+        <v>46171.17877314815</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>46170.8722337963</v>
+        <v>46171.17877314815</v>
       </c>
     </row>
     <row r="10">
@@ -11199,7 +11747,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>[sl 4474.39]</t>
+          <t>[sl 4501.22]</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -11211,13 +11759,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>-20.62</v>
+        <v>10.27</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>46170.92326388889</v>
+        <v>46171.12677083333</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>46170.92326388889</v>
+        <v>46171.12677083333</v>
       </c>
     </row>
     <row r="11">
@@ -11228,25 +11776,25 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>[sl 4498.95]</t>
+          <t>[sl 4501.66]</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>46171.17877314815</v>
+        <v>46174.61928240741</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>46171.17877314815</v>
+        <v>46174.61928240741</v>
       </c>
     </row>
     <row r="12">
@@ -11257,25 +11805,25 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>[sl 4501.22]</t>
+          <t>[sl 4502.92]</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>10.27</v>
+        <v>12.86</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>46171.12677083333</v>
+        <v>46171.40813657407</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>46171.12677083333</v>
+        <v>46171.40813657407</v>
       </c>
     </row>
     <row r="13">
@@ -11286,7 +11834,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>[sl 4501.66]</t>
+          <t>[sl 4509.08]</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -11298,13 +11846,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>2.08</v>
+        <v>20</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>46174.61928240741</v>
+        <v>46174.79511574074</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>46174.61928240741</v>
+        <v>46174.79511574074</v>
       </c>
     </row>
     <row r="14">
@@ -11315,7 +11863,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>[sl 4502.92]</t>
+          <t>[sl 4517.42]</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -11327,13 +11875,13 @@
         <v>1</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>12.86</v>
+        <v>13.69</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>46171.40813657407</v>
+        <v>46174.56412037037</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>46171.40813657407</v>
+        <v>46174.56412037037</v>
       </c>
     </row>
     <row r="15">
@@ -11344,7 +11892,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>[sl 4517.42]</t>
+          <t>[sl 4520.74]</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -11356,13 +11904,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>13.69</v>
+        <v>27.64</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>46174.56412037037</v>
+        <v>46171.56840277778</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>46174.56412037037</v>
+        <v>46171.56840277778</v>
       </c>
     </row>
     <row r="16">
@@ -11373,25 +11921,25 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>[sl 4520.74]</t>
+          <t>[sl 4524.32]</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>27.64</v>
+        <v>12.31</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>46171.56840277778</v>
+        <v>46171.87508101852</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>46171.56840277778</v>
+        <v>46171.87508101852</v>
       </c>
     </row>
     <row r="17">
@@ -11494,20 +12042,20 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D20" s="12" t="n">
         <v>2</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>3.1</v>
+        <v>-6.74</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>46170.60416666666</v>
+        <v>46174.41666666666</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>46178.42708333334</v>
+        <v>46177.23958333334</v>
       </c>
     </row>
     <row r="21">
@@ -11523,20 +12071,20 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>-6.74</v>
+        <v>2.96</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>46174.41666666666</v>
+        <v>46178.42708333334</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>46177.23958333334</v>
+        <v>46178.42708333334</v>
       </c>
     </row>
     <row r="22">
@@ -11601,19 +12149,19 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>[sl 4530.65]</t>
+          <t>[sl 4385.14]</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>45.66</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
@@ -11621,12 +12169,12 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>live_gap</t>
+          <t>live_mismatch</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>[sl 4530.65]</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -11635,17 +12183,13 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>17.72</v>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>46170.92326388889</v>
-      </c>
-      <c r="G25" s="13" t="n">
-        <v>46176.42392361111</v>
-      </c>
+        <v>45.66</v>
+      </c>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -11655,25 +12199,25 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>7.99</v>
+        <v>73.72</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>46170.92326388889</v>
+        <v>46170.39285879629</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>46178.35872685185</v>
+        <v>46176.42392361111</v>
       </c>
     </row>
     <row r="27">
@@ -11684,7 +12228,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -11693,16 +12237,16 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>7.3</v>
+        <v>8.31</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>46170.8722337963</v>
+        <v>46170.92326388889</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>46170.8722337963</v>
+        <v>46178.35872685185</v>
       </c>
     </row>
     <row r="28">
@@ -11713,7 +12257,7 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:ENTRY_TOO_FAR</t>
+          <t>ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -11725,13 +12269,13 @@
         <v>1</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>-1.12</v>
+        <v>12.31</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>46171.87479166667</v>
+        <v>46171.87508101852</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>46171.87479166667</v>
+        <v>46171.87508101852</v>
       </c>
     </row>
     <row r="29">
@@ -11742,7 +12286,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>NEAREST_ALREADY_MATCHED_OR_GREEDY</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -11754,13 +12298,13 @@
         <v>1</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>16.49</v>
+        <v>-1.12</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46171.87479166667</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46171.87479166667</v>
       </c>
     </row>
     <row r="30">
@@ -11771,36 +12315,36 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR</t>
+          <t>NEAREST_ALREADY_MATCHED_OR_GREEDY</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>-18.32</v>
+        <v>16.49</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>46177.17019675926</v>
+        <v>46171.82914351852</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>46177.17019675926</v>
+        <v>46171.82914351852</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>bt_gap</t>
+          <t>live_gap</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -11809,27 +12353,27 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>35.66</v>
+        <v>-18.32</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>46170.60416666666</v>
+        <v>46177.17019675926</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>46178.42708333334</v>
+        <v>46177.17019675926</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>mismatch_gap</t>
+          <t>bt_gap</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>CLOSE_LIFECYCLE_PD</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -11838,16 +12382,16 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>-2.65</v>
+        <v>35.52</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>46170.79517361111</v>
+        <v>46174.41666666666</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>46170.79517361111</v>
+        <v>46178.42708333334</v>
       </c>
     </row>
     <row r="33">
@@ -11858,7 +12402,7 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>LOOSE_MATCH_SL_GUARD</t>
+          <t>CLOSE_LIFECYCLE_PD</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -11870,24 +12414,24 @@
         <v>1</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>45.66</v>
+        <v>-2.65</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46170.79517361111</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46170.79517361111</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>trail_source_gap</t>
+          <t>mismatch_gap</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>- -&gt; M5</t>
+          <t>LOOSE_MATCH_SL_GUARD</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -11899,71 +12443,71 @@
         <v>1</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>-2.65</v>
+        <v>45.66</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>46170.79517361111</v>
+        <v>46171.82914351852</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>46170.79517361111</v>
+        <v>46171.82914351852</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>live_entry_comment</t>
+          <t>mismatch_gap</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>PNL_DIFF_SAME_BUCKET</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>32.47</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>46171.12677083333</v>
+        <v>46170.58363425926</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>46178.35443287037</v>
+        <v>46170.58363425926</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>live_entry_comment</t>
+          <t>trail_source_gap</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>- -&gt; M5</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>17.69</v>
+        <v>-2.65</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>46174.56412037037</v>
+        <v>46170.79517361111</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>46177.34267361111</v>
+        <v>46170.79517361111</v>
       </c>
     </row>
     <row r="37">
@@ -11974,7 +12518,7 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -11983,16 +12527,16 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>-21.42</v>
+        <v>32.47</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>46170.92326388889</v>
+        <v>46171.12677083333</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>46178.35872685185</v>
+        <v>46178.35443287037</v>
       </c>
     </row>
     <row r="38">
@@ -12003,7 +12547,7 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
@@ -12012,16 +12556,16 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>14.54</v>
+        <v>17.69</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>46171.40813657407</v>
+        <v>46174.56412037037</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>46175.65538194445</v>
+        <v>46177.34267361111</v>
       </c>
     </row>
     <row r="39">
@@ -12032,7 +12576,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -12044,13 +12588,13 @@
         <v>3</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>13.92</v>
+        <v>-21.42</v>
       </c>
       <c r="F39" s="13" t="n">
         <v>46170.92326388889</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>46174.66325231481</v>
+        <v>46178.35872685185</v>
       </c>
     </row>
     <row r="40">
@@ -12061,7 +12605,7 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15_M30]_S2</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
@@ -12070,16 +12614,16 @@
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>9.32</v>
+        <v>14.54</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>46171.56840277778</v>
+        <v>46171.40813657407</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>46177.17019675926</v>
+        <v>46175.65538194445</v>
       </c>
     </row>
     <row r="41">
@@ -12090,7 +12634,7 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -12099,16 +12643,16 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.16</v>
+        <v>-14.36</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>46175.5775</v>
+        <v>46174.79511574074</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>46175.5775</v>
+        <v>46177.5493287037</v>
       </c>
     </row>
     <row r="42">
@@ -12119,25 +12663,25 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>[H1_H4_H12]_S2</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>-86.64</v>
+        <v>13.92</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>46174.88290509259</v>
+        <v>46170.92326388889</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>46174.88290509259</v>
+        <v>46174.66325231481</v>
       </c>
     </row>
     <row r="43">
@@ -12148,7 +12692,7 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>[M15_M30_H1]_S2</t>
+          <t>[M5_M15_M30]_S2</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -12157,16 +12701,16 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>5.2</v>
+        <v>9.32</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>46171.98751157407</v>
+        <v>46171.56840277778</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>46171.98751157407</v>
+        <v>46177.17019675926</v>
       </c>
     </row>
     <row r="44">
@@ -12177,7 +12721,7 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>[M1_M5_M15]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -12189,13 +12733,13 @@
         <v>1</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1.52</v>
+        <v>0.16</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>46175.52091435185</v>
+        <v>46175.5775</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>46175.52091435185</v>
+        <v>46175.5775</v>
       </c>
     </row>
     <row r="45">
@@ -12206,25 +12750,25 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>[M1_M5_M15]_S2</t>
+          <t>[M15_H1]_S2</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D45" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>43.32</v>
+        <v>-22.16</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>46170.94866898148</v>
+        <v>46170.39285879629</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>46170.94866898148</v>
+        <v>46170.39285879629</v>
       </c>
     </row>
     <row r="46">
@@ -12235,7 +12779,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>[M30_H1_H4]_S2</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -12247,13 +12791,13 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>7.3</v>
+        <v>12.31</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>46170.8722337963</v>
+        <v>46171.87508101852</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>46170.8722337963</v>
+        <v>46171.87508101852</v>
       </c>
     </row>
     <row r="47">
@@ -12264,25 +12808,25 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15_M30]_S2</t>
+          <t>[M15_M30_H1]_S2</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D47" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>-1.12</v>
+        <v>5.2</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>46171.87479166667</v>
+        <v>46171.98751157407</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>46171.87479166667</v>
+        <v>46171.98751157407</v>
       </c>
     </row>
     <row r="48">
@@ -12293,7 +12837,7 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>[M5_M30_H1]_S2</t>
+          <t>[M1_M5_M15]_S2</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
@@ -12305,24 +12849,24 @@
         <v>1</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>-6.2</v>
+        <v>1.52</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>46175.87108796297</v>
+        <v>46175.52091435185</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>46175.87108796297</v>
+        <v>46175.52091435185</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>mismatch_entry_comment</t>
+          <t>live_entry_comment</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M1_M5_M15]_S2</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -12334,24 +12878,24 @@
         <v>1</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>45.66</v>
+        <v>43.32</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46170.94866898148</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46170.94866898148</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>mismatch_entry_comment</t>
+          <t>live_entry_comment</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>[M5_M15_M30]_S2</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -12363,191 +12907,104 @@
         <v>1</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>-2.65</v>
+        <v>-1.12</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>46170.79517361111</v>
+        <v>46171.87479166667</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>46170.79517361111</v>
+        <v>46171.87479166667</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>live_s14_family</t>
+          <t>mismatch_entry_comment</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>-44.41</v>
+        <v>45.66</v>
       </c>
       <c r="F51" s="13" t="n">
-        <v>46171.40813657407</v>
+        <v>46171.82914351852</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>46177.34267361111</v>
+        <v>46171.82914351852</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>live_s14_family</t>
+          <t>mismatch_entry_comment</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D52" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>74.47</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>46170.8722337963</v>
+        <v>46170.58363425926</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>46178.35872685185</v>
+        <v>46170.58363425926</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>bt_s14_family</t>
+          <t>mismatch_entry_comment</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>42.4</v>
+        <v>-2.65</v>
       </c>
       <c r="F53" s="13" t="n">
-        <v>46170.60416666666</v>
+        <v>46170.79517361111</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>46178.42708333334</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" s="12" t="n">
-        <v>-6.74</v>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>46174.41666666666</v>
-      </c>
-      <c r="G54" s="13" t="n">
-        <v>46177.23958333334</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t>mismatch_s14_family</t>
-        </is>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E55" s="12" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="F55" s="13" t="n">
         <v>46170.79517361111</v>
       </c>
-      <c r="G55" s="13" t="n">
-        <v>46171.82914351852</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>s14_family_mismatch</t>
-        </is>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" s="12" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="F56" s="13" t="n">
-        <v>46170.79517361111</v>
-      </c>
-      <c r="G56" s="13" t="n">
-        <v>46171.82914351852</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G56"/>
+  <autoFilter ref="A1:G53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/excel_reports/backtest_compare/s2/compare_s2_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s2/compare_s2_M15_20260528_0800_20260608_1000.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19 17:35:49</t>
+          <t>2026-06-19 17:57:02</t>
         </is>
       </c>
     </row>

--- a/excel_reports/backtest_compare/s2/compare_s2_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s2/compare_s2_M15_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$CV$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$CV$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$CV$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-21 20:35:10</t>
+          <t>2026-06-22 09:12:58</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -15789,7 +15789,7 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -16197,7 +16197,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -20009,7 +20009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -20808,25 +20808,25 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>30.75</v>
+        <v>-0.05</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>46170.39285879629</v>
+        <v>46170.92326388889</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>46177.17019675926</v>
+        <v>46178.35872685185</v>
       </c>
     </row>
     <row r="29">
@@ -20837,25 +20837,25 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>3.11</v>
+        <v>60.93</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>46170.92326388889</v>
+        <v>46170.39285879629</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>46178.35872685185</v>
+        <v>46174.79511574074</v>
       </c>
     </row>
     <row r="30">
@@ -20866,25 +20866,25 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>ENTRY_TOO_FAR</t>
+          <t>REPLAY_PD_REJECTED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>14.39</v>
+        <v>-30.18</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>46171.87508101852</v>
+        <v>46170.58363425926</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>46174.61928240741</v>
+        <v>46177.17019675926</v>
       </c>
     </row>
     <row r="31">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:ENTRY_TOO_FAR</t>
+          <t>ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -20907,13 +20907,13 @@
         <v>2</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>4.08</v>
+        <v>14.39</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>46171.87479166667</v>
+        <v>46171.87508101852</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>46171.98751157407</v>
+        <v>46174.61928240741</v>
       </c>
     </row>
     <row r="32">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>LIVE_HISTORICAL_TREND_SKIP_DRIFT:ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -20933,16 +20933,16 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>-0.16</v>
+        <v>4.08</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>46176.42392361111</v>
+        <v>46171.87479166667</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>46176.42392361111</v>
+        <v>46171.98751157407</v>
       </c>
     </row>
     <row r="33">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>NEAREST_ALREADY_MATCHED_OR_GREEDY</t>
+          <t>REPLAY_PD_REJECTED:LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -20962,74 +20962,74 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>16.49</v>
+        <v>3.16</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46174.66325231481</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46175.65538194445</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>bt_gap</t>
+          <t>live_gap</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_TREND_SKIP_DRIFT:ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>2.66</v>
+        <v>-0.16</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>46171.75</v>
+        <v>46176.42392361111</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>46181.20833333334</v>
+        <v>46176.42392361111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>bt_gap</t>
+          <t>live_gap</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>ENTRY_TOO_FAR</t>
+          <t>NEAREST_ALREADY_MATCHED_OR_GREEDY</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>-49.12</v>
+        <v>16.49</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>46171.9375</v>
+        <v>46171.82914351852</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>46176.38541666666</v>
+        <v>46171.82914351852</v>
       </c>
     </row>
     <row r="36">
@@ -21040,83 +21040,83 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>-14.18</v>
+        <v>2.66</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>46176.29166666666</v>
+        <v>46171.75</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>46176.29166666666</v>
+        <v>46181.20833333334</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>mismatch_gap</t>
+          <t>bt_gap</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>CLOSE_LIFECYCLE_PD</t>
+          <t>ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>-2.65</v>
+        <v>-49.12</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>46170.79517361111</v>
+        <v>46171.9375</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>46170.79517361111</v>
+        <v>46176.38541666666</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>mismatch_gap</t>
+          <t>bt_gap</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>CLOSE_LIFECYCLE_SL_GUARD</t>
+          <t>TIME_TOO_FAR</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>25.06</v>
+        <v>-14.18</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>46174.56412037037</v>
+        <v>46176.29166666666</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>46174.56412037037</v>
+        <v>46176.29166666666</v>
       </c>
     </row>
     <row r="39">
@@ -21127,7 +21127,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>PNL_DIFF_SAME_BUCKET</t>
+          <t>CLOSE_LIFECYCLE_PD</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -21139,53 +21139,53 @@
         <v>1</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>38.25</v>
+        <v>-2.65</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46170.79517361111</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46170.79517361111</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>trail_source_gap</t>
+          <t>mismatch_gap</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>- -&gt; M5</t>
+          <t>CLOSE_LIFECYCLE_SL_GUARD</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-2.65</v>
+        <v>25.06</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>46170.79517361111</v>
+        <v>46174.56412037037</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>46170.79517361111</v>
+        <v>46174.56412037037</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>live_entry_comment</t>
+          <t>mismatch_gap</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>PNL_DIFF_SAME_BUCKET</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -21194,45 +21194,45 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>32.47</v>
+        <v>38.25</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>46171.12677083333</v>
+        <v>46171.82914351852</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>46178.35443287037</v>
+        <v>46171.82914351852</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>live_entry_comment</t>
+          <t>trail_source_gap</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>[M15_M30]_S2</t>
+          <t>- -&gt; M5</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>-23.4</v>
+        <v>-2.65</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>46170.58363425926</v>
+        <v>46170.79517361111</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>46177.5493287037</v>
+        <v>46170.79517361111</v>
       </c>
     </row>
     <row r="43">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -21252,16 +21252,16 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>-21.42</v>
+        <v>32.47</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>46170.92326388889</v>
+        <v>46171.12677083333</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>46178.35872685185</v>
+        <v>46178.35443287037</v>
       </c>
     </row>
     <row r="44">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>M15_S2_P2</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -21281,16 +21281,16 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>14.54</v>
+        <v>-23.4</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>46171.40813657407</v>
+        <v>46170.58363425926</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>46175.65538194445</v>
+        <v>46177.5493287037</v>
       </c>
     </row>
     <row r="45">
@@ -21301,25 +21301,25 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D45" s="12" t="n">
         <v>3</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>4</v>
+        <v>-21.42</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>46174.61928240741</v>
+        <v>46170.92326388889</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>46177.34267361111</v>
+        <v>46178.35872685185</v>
       </c>
     </row>
     <row r="46">
@@ -21330,25 +21330,25 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>M15_S2_P2</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D46" s="12" t="n">
         <v>3</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>13.92</v>
+        <v>14.54</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>46170.92326388889</v>
+        <v>46171.40813657407</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>46174.66325231481</v>
+        <v>46175.65538194445</v>
       </c>
     </row>
     <row r="47">
@@ -21359,7 +21359,7 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15_M30]_S2</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -21368,16 +21368,16 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>9.32</v>
+        <v>4</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>46171.56840277778</v>
+        <v>46174.61928240741</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>46177.17019675926</v>
+        <v>46177.34267361111</v>
       </c>
     </row>
     <row r="48">
@@ -21388,25 +21388,25 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M5_M15]_S2</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.16</v>
+        <v>13.92</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>46175.5775</v>
+        <v>46170.92326388889</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>46175.5775</v>
+        <v>46174.66325231481</v>
       </c>
     </row>
     <row r="49">
@@ -21417,7 +21417,7 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>[M15_H1]_S2</t>
+          <t>[M5_M15_M30]_S2</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -21426,16 +21426,16 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>-22.16</v>
+        <v>9.32</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>46170.39285879629</v>
+        <v>46171.56840277778</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>46170.39285879629</v>
+        <v>46177.17019675926</v>
       </c>
     </row>
     <row r="50">
@@ -21446,25 +21446,25 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>[M15_M30]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D50" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>12.31</v>
+        <v>0.16</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>46171.87508101852</v>
+        <v>46175.5775</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>46171.87508101852</v>
+        <v>46175.5775</v>
       </c>
     </row>
     <row r="51">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>[M15_M30_H1]_S2</t>
+          <t>[M15_H1]_S2</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -21487,13 +21487,13 @@
         <v>1</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>5.2</v>
+        <v>-22.16</v>
       </c>
       <c r="F51" s="13" t="n">
-        <v>46171.98751157407</v>
+        <v>46170.39285879629</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>46171.98751157407</v>
+        <v>46170.39285879629</v>
       </c>
     </row>
     <row r="52">
@@ -21504,25 +21504,25 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>[M1_M5_M15]_S2</t>
+          <t>[M15_M30]_S2</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D52" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>1.52</v>
+        <v>12.31</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>46175.52091435185</v>
+        <v>46171.87508101852</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>46175.52091435185</v>
+        <v>46171.87508101852</v>
       </c>
     </row>
     <row r="53">
@@ -21533,25 +21533,25 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>[M1_M5_M15]_S2</t>
+          <t>[M15_M30_H1]_S2</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D53" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>43.32</v>
+        <v>5.2</v>
       </c>
       <c r="F53" s="13" t="n">
-        <v>46170.94866898148</v>
+        <v>46171.98751157407</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>46170.94866898148</v>
+        <v>46171.98751157407</v>
       </c>
     </row>
     <row r="54">
@@ -21562,36 +21562,36 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15_M30]_S2</t>
+          <t>[M1_M5_M15]_S2</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D54" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>-1.12</v>
+        <v>1.52</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>46171.87479166667</v>
+        <v>46175.52091435185</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>46171.87479166667</v>
+        <v>46175.52091435185</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>mismatch_entry_comment</t>
+          <t>live_entry_comment</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>M15_S2_P1</t>
+          <t>[M1_M5_M15]_S2</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -21603,42 +21603,42 @@
         <v>1</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>38.25</v>
+        <v>43.32</v>
       </c>
       <c r="F55" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46170.94866898148</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>46171.82914351852</v>
+        <v>46170.94866898148</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>mismatch_entry_comment</t>
+          <t>live_entry_comment</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>[M5_M15_M30]_S2</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D56" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>25.06</v>
+        <v>-1.12</v>
       </c>
       <c r="F56" s="13" t="n">
-        <v>46174.56412037037</v>
+        <v>46171.87479166667</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>46174.56412037037</v>
+        <v>46171.87479166667</v>
       </c>
     </row>
     <row r="57">
@@ -21649,7 +21649,7 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>[M5_M15]_S2</t>
+          <t>M15_S2_P1</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -21661,17 +21661,75 @@
         <v>1</v>
       </c>
       <c r="E57" s="12" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>46171.82914351852</v>
+      </c>
+      <c r="G57" s="13" t="n">
+        <v>46171.82914351852</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>mismatch_entry_comment</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>[M5_M15]_S2</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>46174.56412037037</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>46174.56412037037</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>mismatch_entry_comment</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>[M5_M15]_S2</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="12" t="n">
         <v>-2.65</v>
       </c>
-      <c r="F57" s="13" t="n">
+      <c r="F59" s="13" t="n">
         <v>46170.79517361111</v>
       </c>
-      <c r="G57" s="13" t="n">
+      <c r="G59" s="13" t="n">
         <v>46170.79517361111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G57"/>
+  <autoFilter ref="A1:G59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>